--- a/model/Outputs/11. Interest rate/20/Output Files/0.1/Output_18_47.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.1/Output_18_47.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5717662.902390701</v>
+        <v>5717790.953753825</v>
       </c>
     </row>
     <row r="7">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39020031.84654357</v>
+        <v>39020031.84654358</v>
       </c>
     </row>
   </sheetData>
@@ -660,7 +660,7 @@
         <v>42.47457824299391</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3.339155739849787</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>60.76287729833814</v>
+        <v>57.42372155848824</v>
       </c>
       <c r="T2" t="n">
         <v>178.4965164019308</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>287.4867555439494</v>
+        <v>57.45968638709719</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>212.1645934385184</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -793,10 +793,10 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>7.510667191520156</v>
+        <v>346</v>
       </c>
       <c r="W3" t="n">
-        <v>346</v>
+        <v>25.37314290982852</v>
       </c>
       <c r="X3" t="n">
         <v>12.86273944538755</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>74.99931295557451</v>
+        <v>50.71260540520722</v>
       </c>
       <c r="C5" t="n">
         <v>42.47457824299391</v>
@@ -948,7 +948,7 @@
         <v>178.4965164019308</v>
       </c>
       <c r="U5" t="n">
-        <v>217.9130412595499</v>
+        <v>242.1997488099172</v>
       </c>
       <c r="V5" t="n">
         <v>222.8510241668239</v>
@@ -970,16 +970,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>154.6833405621777</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>346</v>
+        <v>205.4509928893978</v>
       </c>
       <c r="S6" t="n">
-        <v>346</v>
+        <v>56.88716034196977</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>111.8375770826228</v>
+        <v>7.510667191520156</v>
       </c>
       <c r="W6" t="n">
         <v>25.37314290982852</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>74.99931295557451</v>
+        <v>73.9974054052072</v>
       </c>
       <c r="C8" t="n">
         <v>42.47457824299391</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>80.70852155848823</v>
+        <v>81.71042910885556</v>
       </c>
       <c r="T8" t="n">
         <v>178.4965164019307</v>
@@ -1207,16 +1207,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>352.000000000006</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>352.000000000006</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1255,22 +1255,22 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>131.3261369150208</v>
+        <v>194.4945572042193</v>
       </c>
       <c r="S9" t="n">
-        <v>136.1008207629216</v>
+        <v>56.88716034196979</v>
       </c>
       <c r="T9" t="n">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>7.510667191520156</v>
       </c>
       <c r="W9" t="n">
-        <v>352</v>
+        <v>25.37314290982852</v>
       </c>
       <c r="X9" t="n">
         <v>12.86273944538755</v>
@@ -1380,10 +1380,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G11" t="n">
-        <v>3.488025553347868</v>
+        <v>3.488025553347882</v>
       </c>
       <c r="H11" t="n">
-        <v>5.251211467346504</v>
+        <v>5.251211467346479</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1416,10 +1416,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>26.88196622291339</v>
+        <v>88.71042910885558</v>
       </c>
       <c r="T11" t="n">
-        <v>185.4965164019307</v>
+        <v>185.4965164019308</v>
       </c>
       <c r="U11" t="n">
         <v>249.1997488099172</v>
@@ -1428,7 +1428,7 @@
         <v>229.8510241668239</v>
       </c>
       <c r="W11" t="n">
-        <v>238.3734759809475</v>
+        <v>176.5450130950053</v>
       </c>
       <c r="X11" t="n">
         <v>192.2818334606677</v>
@@ -1444,16 +1444,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>359.0000000000137</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1492,28 +1492,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>359</v>
+        <v>138.3261369150208</v>
       </c>
       <c r="S12" t="n">
-        <v>227.449191190808</v>
+        <v>63.88716034196977</v>
       </c>
       <c r="T12" t="n">
-        <v>4.776887859023249</v>
+        <v>4.776887859023248</v>
       </c>
       <c r="U12" t="n">
-        <v>0.200878628111276</v>
+        <v>0.2008786281112975</v>
       </c>
       <c r="V12" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W12" t="n">
-        <v>359</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X12" t="n">
-        <v>19.86273944538755</v>
+        <v>29.05339324743627</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>359.0000000000137</v>
       </c>
     </row>
     <row r="13">
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>5.585037993844747</v>
+        <v>5.585037993844765</v>
       </c>
       <c r="M13" t="n">
         <v>101.6925786156646</v>
@@ -1605,7 +1605,7 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D14" t="n">
         <v>10.33915573984979</v>
@@ -1614,13 +1614,13 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G14" t="n">
-        <v>3.488025553347882</v>
+        <v>3.488025553347868</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>5.251211467346504</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1653,13 +1653,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>88.71042910885558</v>
+        <v>88.71042910885556</v>
       </c>
       <c r="T14" t="n">
-        <v>185.4965164019308</v>
+        <v>123.6680535159884</v>
       </c>
       <c r="U14" t="n">
-        <v>246.9867043423272</v>
+        <v>249.1997488099172</v>
       </c>
       <c r="V14" t="n">
         <v>229.8510241668239</v>
@@ -1681,13 +1681,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>359.0000000000092</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>45.09863337917722</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1732,25 +1732,25 @@
         <v>138.3261369150208</v>
       </c>
       <c r="S15" t="n">
-        <v>63.88716034196977</v>
+        <v>63.88716034196979</v>
       </c>
       <c r="T15" t="n">
-        <v>4.776887859023248</v>
+        <v>4.776887859023249</v>
       </c>
       <c r="U15" t="n">
-        <v>359</v>
+        <v>0.200878628111276</v>
       </c>
       <c r="V15" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W15" t="n">
-        <v>45.29951200731641</v>
+        <v>359.0000000000092</v>
       </c>
       <c r="X15" t="n">
-        <v>359</v>
+        <v>359.0000000000092</v>
       </c>
       <c r="Y15" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>5.585037993844765</v>
+        <v>5.585037993844747</v>
       </c>
       <c r="M16" t="n">
         <v>101.6925786156646</v>
@@ -1851,13 +1851,13 @@
         <v>0.3632896068686478</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.8896287080118555</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5017861551637537</v>
+        <v>0.5017861551679884</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1893,10 +1893,10 @@
         <v>84.71042910885556</v>
       </c>
       <c r="T17" t="n">
-        <v>177.2969192446946</v>
+        <v>181.4965164019307</v>
       </c>
       <c r="U17" t="n">
-        <v>245.1997488099172</v>
+        <v>240.1105229446692</v>
       </c>
       <c r="V17" t="n">
         <v>225.8510241668239</v>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>359.0000000000093</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -1966,10 +1966,10 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>359</v>
+        <v>134.3261369150208</v>
       </c>
       <c r="S18" t="n">
-        <v>59.88716034196979</v>
+        <v>92.81352943942956</v>
       </c>
       <c r="T18" t="n">
         <v>0.7768878590232496</v>
@@ -1978,16 +1978,16 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>177.7631732040287</v>
+        <v>10.51066719152016</v>
       </c>
       <c r="W18" t="n">
         <v>28.37314290982852</v>
       </c>
       <c r="X18" t="n">
-        <v>359</v>
+        <v>359.0000000000093</v>
       </c>
       <c r="Y18" t="n">
-        <v>359</v>
+        <v>359.0000000000093</v>
       </c>
     </row>
     <row r="19">
@@ -2094,7 +2094,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.251211467346504</v>
+        <v>1.251211467346479</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>78.87177793143236</v>
+        <v>78.87177793143168</v>
       </c>
       <c r="T20" t="n">
-        <v>181.4965164019307</v>
+        <v>181.4965164019308</v>
       </c>
       <c r="U20" t="n">
         <v>245.1997488099172</v>
@@ -2158,16 +2158,16 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>359.0000000000093</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>212.1645934385184</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2200,16 +2200,16 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>154.6833405621777</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>359</v>
+        <v>181.8158373315318</v>
       </c>
       <c r="S21" t="n">
-        <v>359</v>
+        <v>59.88716034196977</v>
       </c>
       <c r="T21" t="n">
-        <v>204.205880767418</v>
+        <v>0.7768878590232475</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2264,10 +2264,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1.585037993844747</v>
+        <v>1.585037993844765</v>
       </c>
       <c r="M22" t="n">
-        <v>97.69257861566464</v>
+        <v>97.69257861566462</v>
       </c>
       <c r="N22" t="n">
         <v>148.6963703536521</v>
@@ -2331,7 +2331,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.251211467346479</v>
+        <v>0.5017861551637537</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>78.87177793143101</v>
+        <v>84.71042910885556</v>
       </c>
       <c r="T23" t="n">
-        <v>181.4965164019308</v>
+        <v>181.4965164019307</v>
       </c>
       <c r="U23" t="n">
         <v>245.1997488099172</v>
@@ -2376,7 +2376,7 @@
         <v>225.8510241668239</v>
       </c>
       <c r="W23" t="n">
-        <v>234.3734759809475</v>
+        <v>229.2842501156996</v>
       </c>
       <c r="X23" t="n">
         <v>188.2818334606677</v>
@@ -2395,16 +2395,16 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>63.81760319460793</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -2443,19 +2443,19 @@
         <v>134.3261369150208</v>
       </c>
       <c r="S24" t="n">
-        <v>115.8346000954187</v>
+        <v>59.88716034196979</v>
       </c>
       <c r="T24" t="n">
-        <v>0.7768878590232475</v>
+        <v>0.7768878590232496</v>
       </c>
       <c r="U24" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>359</v>
+        <v>10.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>359</v>
+        <v>28.37314290982852</v>
       </c>
       <c r="X24" t="n">
         <v>15.86273944538755</v>
@@ -2501,10 +2501,10 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1.585037993844765</v>
+        <v>1.585037993844747</v>
       </c>
       <c r="M25" t="n">
-        <v>97.69257861566462</v>
+        <v>97.69257861566464</v>
       </c>
       <c r="N25" t="n">
         <v>148.6963703536521</v>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>125.9993129555745</v>
       </c>
       <c r="C26" t="n">
         <v>93.47457824299391</v>
@@ -2568,7 +2568,7 @@
         <v>47.48802555334788</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>49.25121146734648</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2607,16 +2607,16 @@
         <v>229.4965164019308</v>
       </c>
       <c r="U26" t="n">
-        <v>293.1997488099172</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>273.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>113.8606000874497</v>
+        <v>269.379015180602</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>236.2818334606677</v>
       </c>
       <c r="Y26" t="n">
         <v>155.3174326828064</v>
@@ -2632,7 +2632,7 @@
         <v>28.55655664632661</v>
       </c>
       <c r="C27" t="n">
-        <v>5.099912445519294</v>
+        <v>350.0000000000234</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -2680,13 +2680,13 @@
         <v>182.3261369150208</v>
       </c>
       <c r="S27" t="n">
-        <v>350</v>
+        <v>146.5788498124741</v>
       </c>
       <c r="T27" t="n">
-        <v>350</v>
+        <v>350.0000000000234</v>
       </c>
       <c r="U27" t="n">
-        <v>185.6798159951128</v>
+        <v>44.2008786281113</v>
       </c>
       <c r="V27" t="n">
         <v>58.51066719152016</v>
@@ -2744,19 +2744,19 @@
         <v>145.6925786156646</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>196.6963703536521</v>
       </c>
       <c r="O28" t="n">
-        <v>191.4841918941862</v>
+        <v>267.3682526036051</v>
       </c>
       <c r="P28" t="n">
-        <v>316.835307164343</v>
+        <v>44.25487610122502</v>
       </c>
       <c r="Q28" t="n">
-        <v>350</v>
+        <v>350.0000000000234</v>
       </c>
       <c r="R28" t="n">
-        <v>350</v>
+        <v>350.0000000000234</v>
       </c>
       <c r="S28" t="n">
         <v>4.267922325806239</v>
@@ -2790,19 +2790,19 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>87.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>48.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>42.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>42.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>41.48802555334787</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>43.2512114673465</v>
@@ -2841,7 +2841,7 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>223.4965164019307</v>
+        <v>61.11564472347898</v>
       </c>
       <c r="U29" t="n">
         <v>287.1997488099172</v>
@@ -2853,10 +2853,10 @@
         <v>276.3734759809475</v>
       </c>
       <c r="X29" t="n">
-        <v>40.44297402997378</v>
+        <v>230.2818334606677</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>149.3174326828064</v>
       </c>
     </row>
     <row r="30">
@@ -2869,7 +2869,7 @@
         <v>22.55655664632661</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>200.9739511752674</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>330.7762569977419</v>
       </c>
       <c r="I30" t="n">
         <v>212.1645934385184</v>
@@ -2914,19 +2914,19 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>350</v>
+        <v>176.3261369150208</v>
       </c>
       <c r="S30" t="n">
         <v>101.8871603419698</v>
       </c>
       <c r="T30" t="n">
-        <v>350</v>
+        <v>42.77688785902325</v>
       </c>
       <c r="U30" t="n">
         <v>38.20087862811128</v>
       </c>
       <c r="V30" t="n">
-        <v>103.3639001385737</v>
+        <v>52.51066719152016</v>
       </c>
       <c r="W30" t="n">
         <v>70.37314290982852</v>
@@ -2978,10 +2978,10 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>139.6925786156646</v>
       </c>
       <c r="N31" t="n">
-        <v>86.07644023205191</v>
+        <v>190.6963703536521</v>
       </c>
       <c r="O31" t="n">
         <v>261.3682526036051</v>
@@ -2990,10 +2990,10 @@
         <v>310.835307164343</v>
       </c>
       <c r="Q31" t="n">
-        <v>350</v>
+        <v>105.6874912627175</v>
       </c>
       <c r="R31" t="n">
-        <v>350</v>
+        <v>350.0000000000175</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>71.99931295557451</v>
+        <v>69.95100540520718</v>
       </c>
       <c r="C32" t="n">
         <v>39.47457824299391</v>
@@ -3081,7 +3081,7 @@
         <v>175.4965164019307</v>
       </c>
       <c r="U32" t="n">
-        <v>237.1514412595499</v>
+        <v>239.1997488099172</v>
       </c>
       <c r="V32" t="n">
         <v>219.8510241668239</v>
@@ -3121,7 +3121,7 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>330.7762569977419</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3151,22 +3151,22 @@
         <v>154.6833405621777</v>
       </c>
       <c r="R33" t="n">
-        <v>344</v>
+        <v>128.3261369150208</v>
       </c>
       <c r="S33" t="n">
         <v>53.88716034196979</v>
       </c>
       <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
         <v>344</v>
       </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
       <c r="V33" t="n">
-        <v>4.510667191520156</v>
+        <v>344</v>
       </c>
       <c r="W33" t="n">
-        <v>93.27503546120279</v>
+        <v>300.2358227354439</v>
       </c>
       <c r="X33" t="n">
         <v>9.862739445387547</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>73.83567729833818</v>
+        <v>75.71042910885556</v>
       </c>
       <c r="T35" t="n">
         <v>172.4965164019307</v>
@@ -3330,7 +3330,7 @@
         <v>179.2818334606677</v>
       </c>
       <c r="Y35" t="n">
-        <v>98.31743268280638</v>
+        <v>96.44268087228882</v>
       </c>
     </row>
     <row r="36">
@@ -3349,10 +3349,10 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>63.51254954911638</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3388,19 +3388,19 @@
         <v>154.6833405621777</v>
       </c>
       <c r="R36" t="n">
-        <v>125.3261369150208</v>
+        <v>337</v>
       </c>
       <c r="S36" t="n">
         <v>50.88716034196979</v>
       </c>
       <c r="T36" t="n">
-        <v>276.6970798256156</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>337</v>
+        <v>1.510667191520156</v>
       </c>
       <c r="W36" t="n">
         <v>19.37314290982852</v>
@@ -3464,10 +3464,10 @@
         <v>259.835307164343</v>
       </c>
       <c r="Q37" t="n">
-        <v>302.722266425598</v>
+        <v>301.0674550848626</v>
       </c>
       <c r="R37" t="n">
-        <v>306.5148248371369</v>
+        <v>308.1696361778723</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>68.99931295557451</v>
       </c>
       <c r="C38" t="n">
-        <v>36.47457824299391</v>
+        <v>34.59982643247634</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -3549,10 +3549,10 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>73.83567729833818</v>
+        <v>75.71042910885558</v>
       </c>
       <c r="T38" t="n">
-        <v>172.4965164019307</v>
+        <v>172.4965164019308</v>
       </c>
       <c r="U38" t="n">
         <v>236.1997488099172</v>
@@ -3586,16 +3586,16 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>330.7762569977419</v>
+        <v>275.1864126340955</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3628,16 +3628,16 @@
         <v>125.3261369150208</v>
       </c>
       <c r="S39" t="n">
-        <v>50.88716034196979</v>
+        <v>50.88716034196977</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>282.9208228278737</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>337</v>
+        <v>1.510667191520156</v>
       </c>
       <c r="W39" t="n">
         <v>19.37314290982852</v>
@@ -3689,7 +3689,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>88.69257861566464</v>
+        <v>87.03776727492934</v>
       </c>
       <c r="N40" t="n">
         <v>139.6963703536521</v>
@@ -3701,7 +3701,7 @@
         <v>259.835307164343</v>
       </c>
       <c r="Q40" t="n">
-        <v>301.0674550848626</v>
+        <v>302.722266425598</v>
       </c>
       <c r="R40" t="n">
         <v>308.1696361778723</v>
@@ -3744,16 +3744,16 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>54.77648531360494</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>91.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>90.48802555334787</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>92.25121146734651</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3786,10 +3786,10 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>56.90883464038062</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>272.4965164019307</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>336.1997488099172</v>
@@ -3826,13 +3826,13 @@
         <v>29.67209722191262</v>
       </c>
       <c r="F42" t="n">
-        <v>26.63624233787687</v>
+        <v>123.862661066321</v>
       </c>
       <c r="G42" t="n">
         <v>12.59542266748017</v>
       </c>
       <c r="H42" t="n">
-        <v>115.002675726186</v>
+        <v>17.77625699774189</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3923,25 +3923,25 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>92.58503799384475</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>188.6925786156646</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>239.6963703536521</v>
       </c>
       <c r="O43" t="n">
-        <v>249.5616776741938</v>
+        <v>310.3682526036051</v>
       </c>
       <c r="P43" t="n">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>337</v>
       </c>
       <c r="R43" t="n">
-        <v>337</v>
+        <v>92.21943810742711</v>
       </c>
       <c r="S43" t="n">
         <v>47.26792232580625</v>
@@ -3975,10 +3975,10 @@
         <v>174.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>142.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>103.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -3987,10 +3987,10 @@
         <v>97.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>96.48802555334787</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>98.25121146734651</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4029,19 +4029,19 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>26.63096308408387</v>
       </c>
       <c r="X44" t="n">
         <v>285.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>127.3954247633522</v>
+        <v>204.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -4169,19 +4169,19 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>316.3682526036051</v>
       </c>
       <c r="P46" t="n">
-        <v>251.4943104586566</v>
+        <v>337</v>
       </c>
       <c r="Q46" t="n">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>337</v>
+        <v>218.8581355292453</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>53.26792232580625</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70.58361438686254</v>
+        <v>73.95649897256939</v>
       </c>
       <c r="C2" t="n">
-        <v>27.68</v>
+        <v>31.05288458570686</v>
       </c>
       <c r="D2" t="n">
         <v>27.68</v>
@@ -4321,25 +4321,25 @@
         <v>27.68</v>
       </c>
       <c r="J2" t="n">
-        <v>27.68</v>
+        <v>370.22</v>
       </c>
       <c r="K2" t="n">
-        <v>61.59929542713568</v>
+        <v>404.1392954271357</v>
       </c>
       <c r="L2" t="n">
-        <v>103.6791807537689</v>
+        <v>660.8591164251993</v>
       </c>
       <c r="M2" t="n">
-        <v>446.2191807537689</v>
+        <v>660.8591164251993</v>
       </c>
       <c r="N2" t="n">
-        <v>788.759180753769</v>
+        <v>1003.399116425199</v>
       </c>
       <c r="O2" t="n">
-        <v>788.759180753769</v>
+        <v>1003.399116425199</v>
       </c>
       <c r="P2" t="n">
-        <v>1131.299180753769</v>
+        <v>1041.46</v>
       </c>
       <c r="Q2" t="n">
         <v>1384</v>
@@ -4348,25 +4348,25 @@
         <v>1384</v>
       </c>
       <c r="S2" t="n">
-        <v>1322.623356264305</v>
+        <v>1325.996240850012</v>
       </c>
       <c r="T2" t="n">
-        <v>1142.323844747203</v>
+        <v>1145.69672933291</v>
       </c>
       <c r="U2" t="n">
-        <v>897.6776338280949</v>
+        <v>901.0505184138018</v>
       </c>
       <c r="V2" t="n">
-        <v>672.5755892151415</v>
+        <v>675.9484738008483</v>
       </c>
       <c r="W2" t="n">
-        <v>438.8650074162045</v>
+        <v>442.2378920019114</v>
       </c>
       <c r="X2" t="n">
-        <v>251.711640284217</v>
+        <v>255.0845248699238</v>
       </c>
       <c r="Y2" t="n">
-        <v>146.3404961601701</v>
+        <v>149.713380745877</v>
       </c>
     </row>
     <row r="3">
@@ -4376,34 +4376,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>318.0706621655798</v>
+        <v>300.0277573996117</v>
       </c>
       <c r="C3" t="n">
-        <v>318.0706621655798</v>
+        <v>300.0277573996117</v>
       </c>
       <c r="D3" t="n">
-        <v>27.67999999997437</v>
+        <v>241.9876701399176</v>
       </c>
       <c r="E3" t="n">
-        <v>27.67999999997437</v>
+        <v>241.9876701399176</v>
       </c>
       <c r="F3" t="n">
-        <v>27.67999999997437</v>
+        <v>241.9876701399176</v>
       </c>
       <c r="G3" t="n">
-        <v>27.67999999997437</v>
+        <v>241.9876701399176</v>
       </c>
       <c r="H3" t="n">
-        <v>27.67999999997437</v>
+        <v>241.9876701399176</v>
       </c>
       <c r="I3" t="n">
-        <v>27.67999999997437</v>
+        <v>27.68</v>
       </c>
       <c r="J3" t="n">
-        <v>165.1159025337639</v>
+        <v>165.1159025337895</v>
       </c>
       <c r="K3" t="n">
-        <v>377.3471300432416</v>
+        <v>377.3471300432673</v>
       </c>
       <c r="L3" t="n">
         <v>678.6214735340828</v>
@@ -4436,16 +4436,16 @@
         <v>1037.639759778618</v>
       </c>
       <c r="V3" t="n">
-        <v>1030.053227261931</v>
+        <v>688.1448102836683</v>
       </c>
       <c r="W3" t="n">
-        <v>680.5582777669814</v>
+        <v>662.5153730010132</v>
       </c>
       <c r="X3" t="n">
-        <v>667.5656116605294</v>
+        <v>649.5227068945612</v>
       </c>
       <c r="Y3" t="n">
-        <v>667.5656116605294</v>
+        <v>649.5227068945612</v>
       </c>
     </row>
     <row r="4">
@@ -4455,34 +4455,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>742.177048241729</v>
+        <v>901.2408214272289</v>
       </c>
       <c r="C4" t="n">
-        <v>875.1090540601648</v>
+        <v>1034.172827245665</v>
       </c>
       <c r="D4" t="n">
-        <v>995.3581981851648</v>
+        <v>1154.421971370665</v>
       </c>
       <c r="E4" t="n">
-        <v>1120.117102396578</v>
+        <v>1279.180875582078</v>
       </c>
       <c r="F4" t="n">
-        <v>1251.408074988513</v>
+        <v>1279.180875582078</v>
       </c>
       <c r="G4" t="n">
-        <v>1251.408074988513</v>
+        <v>1279.180875582078</v>
       </c>
       <c r="H4" t="n">
-        <v>1251.408074988513</v>
+        <v>1279.180875582078</v>
       </c>
       <c r="I4" t="n">
-        <v>1251.408074988513</v>
+        <v>1384</v>
       </c>
       <c r="J4" t="n">
-        <v>1251.408074988513</v>
+        <v>1384</v>
       </c>
       <c r="K4" t="n">
-        <v>1382.599187613906</v>
+        <v>1384</v>
       </c>
       <c r="L4" t="n">
         <v>1384</v>
@@ -4512,19 +4512,19 @@
         <v>73.94475689745182</v>
       </c>
       <c r="U4" t="n">
-        <v>168.3687006125337</v>
+        <v>327.4324737980335</v>
       </c>
       <c r="V4" t="n">
-        <v>168.3687006125337</v>
+        <v>327.4324737980335</v>
       </c>
       <c r="W4" t="n">
-        <v>347.1896188722111</v>
+        <v>506.2533920577109</v>
       </c>
       <c r="X4" t="n">
-        <v>505.1504098964047</v>
+        <v>664.2141830819045</v>
       </c>
       <c r="Y4" t="n">
-        <v>623.4897105754369</v>
+        <v>782.5534837609367</v>
       </c>
     </row>
     <row r="5">
@@ -4558,25 +4558,25 @@
         <v>27.68</v>
       </c>
       <c r="J5" t="n">
-        <v>27.68</v>
+        <v>242.3199356714304</v>
       </c>
       <c r="K5" t="n">
-        <v>61.59929542713568</v>
+        <v>276.2392310985661</v>
       </c>
       <c r="L5" t="n">
-        <v>103.6791807537689</v>
+        <v>318.3191164251993</v>
       </c>
       <c r="M5" t="n">
-        <v>446.2191807537689</v>
+        <v>660.8591164251993</v>
       </c>
       <c r="N5" t="n">
-        <v>788.759180753769</v>
+        <v>1003.399116425199</v>
       </c>
       <c r="O5" t="n">
-        <v>1131.299180753769</v>
+        <v>1003.399116425199</v>
       </c>
       <c r="P5" t="n">
-        <v>1169.36006432857</v>
+        <v>1041.46</v>
       </c>
       <c r="Q5" t="n">
         <v>1384</v>
@@ -4591,19 +4591,19 @@
         <v>1121.164701504256</v>
       </c>
       <c r="U5" t="n">
-        <v>901.0505184138018</v>
+        <v>876.518490585148</v>
       </c>
       <c r="V5" t="n">
-        <v>675.9484738008483</v>
+        <v>651.4164459721945</v>
       </c>
       <c r="W5" t="n">
-        <v>442.2378920019114</v>
+        <v>417.7058641732576</v>
       </c>
       <c r="X5" t="n">
-        <v>255.0845248699238</v>
+        <v>230.55249704127</v>
       </c>
       <c r="Y5" t="n">
-        <v>149.713380745877</v>
+        <v>125.1813529172232</v>
       </c>
     </row>
     <row r="6">
@@ -4613,13 +4613,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.68</v>
+        <v>723.308381032235</v>
       </c>
       <c r="C6" t="n">
-        <v>27.68</v>
+        <v>373.8134315372855</v>
       </c>
       <c r="D6" t="n">
-        <v>27.68</v>
+        <v>373.8134315372855</v>
       </c>
       <c r="E6" t="n">
         <v>27.68</v>
@@ -4658,31 +4658,31 @@
         <v>1384.000000000017</v>
       </c>
       <c r="Q6" t="n">
-        <v>1227.754201452363</v>
+        <v>1384.000000000017</v>
       </c>
       <c r="R6" t="n">
-        <v>878.2592519574131</v>
+        <v>1176.473744556181</v>
       </c>
       <c r="S6" t="n">
-        <v>528.7643024624635</v>
+        <v>1119.011966432979</v>
       </c>
       <c r="T6" t="n">
-        <v>528.7643024624635</v>
+        <v>1119.011966432979</v>
       </c>
       <c r="U6" t="n">
-        <v>179.269352967514</v>
+        <v>1119.011966432979</v>
       </c>
       <c r="V6" t="n">
-        <v>66.30210338910715</v>
+        <v>1111.425433916292</v>
       </c>
       <c r="W6" t="n">
-        <v>40.67266610645207</v>
+        <v>1085.795996633637</v>
       </c>
       <c r="X6" t="n">
-        <v>27.68</v>
+        <v>1072.803330527185</v>
       </c>
       <c r="Y6" t="n">
-        <v>27.68</v>
+        <v>1072.803330527185</v>
       </c>
     </row>
     <row r="7">
@@ -4692,28 +4692,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>847.3879507221912</v>
+        <v>73.94475689745182</v>
       </c>
       <c r="C7" t="n">
-        <v>847.3879507221912</v>
+        <v>73.94475689745182</v>
       </c>
       <c r="D7" t="n">
-        <v>847.3879507221912</v>
+        <v>83.19205869460247</v>
       </c>
       <c r="E7" t="n">
-        <v>972.1468549336042</v>
+        <v>207.9509629060155</v>
       </c>
       <c r="F7" t="n">
-        <v>1103.43782752554</v>
+        <v>339.241935497951</v>
       </c>
       <c r="G7" t="n">
-        <v>1103.43782752554</v>
+        <v>499.6981128602461</v>
       </c>
       <c r="H7" t="n">
-        <v>1103.43782752554</v>
+        <v>677.208152773742</v>
       </c>
       <c r="I7" t="n">
-        <v>1103.43782752554</v>
+        <v>908.8680749885134</v>
       </c>
       <c r="J7" t="n">
         <v>1251.408074988513</v>
@@ -4746,22 +4746,22 @@
         <v>73.94475689745182</v>
       </c>
       <c r="T7" t="n">
-        <v>269.4615032693715</v>
+        <v>73.94475689745182</v>
       </c>
       <c r="U7" t="n">
-        <v>522.9492201699532</v>
+        <v>73.94475689745182</v>
       </c>
       <c r="V7" t="n">
-        <v>728.7006130558991</v>
+        <v>73.94475689745182</v>
       </c>
       <c r="W7" t="n">
-        <v>728.7006130558991</v>
+        <v>73.94475689745182</v>
       </c>
       <c r="X7" t="n">
-        <v>728.7006130558991</v>
+        <v>73.94475689745182</v>
       </c>
       <c r="Y7" t="n">
-        <v>728.7006130558991</v>
+        <v>73.94475689745182</v>
       </c>
     </row>
     <row r="8">
@@ -4795,25 +4795,25 @@
         <v>28.16</v>
       </c>
       <c r="J8" t="n">
-        <v>376.64</v>
+        <v>376.640000000006</v>
       </c>
       <c r="K8" t="n">
-        <v>410.5592954271357</v>
+        <v>410.5592954271417</v>
       </c>
       <c r="L8" t="n">
-        <v>452.6391807537689</v>
+        <v>452.6391807537749</v>
       </c>
       <c r="M8" t="n">
-        <v>801.1191807537689</v>
+        <v>801.1191807537809</v>
       </c>
       <c r="N8" t="n">
-        <v>1149.599180753769</v>
+        <v>1149.599180753787</v>
       </c>
       <c r="O8" t="n">
-        <v>1149.599180753769</v>
+        <v>1149.599180753787</v>
       </c>
       <c r="P8" t="n">
-        <v>1187.66006432857</v>
+        <v>1187.660064328588</v>
       </c>
       <c r="Q8" t="n">
         <v>1408</v>
@@ -4822,25 +4822,25 @@
         <v>1408</v>
       </c>
       <c r="S8" t="n">
-        <v>1326.476240850012</v>
+        <v>1325.464213021358</v>
       </c>
       <c r="T8" t="n">
-        <v>1146.17672933291</v>
+        <v>1145.164701504256</v>
       </c>
       <c r="U8" t="n">
-        <v>901.5305184138018</v>
+        <v>900.518490585148</v>
       </c>
       <c r="V8" t="n">
-        <v>676.4284738008483</v>
+        <v>675.4164459721945</v>
       </c>
       <c r="W8" t="n">
-        <v>442.7178920019114</v>
+        <v>441.7058641732576</v>
       </c>
       <c r="X8" t="n">
-        <v>255.5645248699238</v>
+        <v>254.55249704127</v>
       </c>
       <c r="Y8" t="n">
-        <v>150.193380745877</v>
+        <v>149.1813529172231</v>
       </c>
     </row>
     <row r="9">
@@ -4850,13 +4850,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28.16</v>
+        <v>729.8489870928472</v>
       </c>
       <c r="C9" t="n">
-        <v>28.16</v>
+        <v>374.2934315372855</v>
       </c>
       <c r="D9" t="n">
-        <v>28.16</v>
+        <v>374.2934315372855</v>
       </c>
       <c r="E9" t="n">
         <v>28.16</v>
@@ -4898,28 +4898,28 @@
         <v>1385.534105368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1252.88144181801</v>
+        <v>1189.074956677405</v>
       </c>
       <c r="S9" t="n">
-        <v>1115.405865289806</v>
+        <v>1131.613178554203</v>
       </c>
       <c r="T9" t="n">
-        <v>759.8503097342502</v>
+        <v>1131.613178554203</v>
       </c>
       <c r="U9" t="n">
-        <v>404.2947541786947</v>
+        <v>1131.613178554203</v>
       </c>
       <c r="V9" t="n">
-        <v>396.7082216620076</v>
+        <v>1124.026646037516</v>
       </c>
       <c r="W9" t="n">
-        <v>41.15266610645207</v>
+        <v>1098.397208754861</v>
       </c>
       <c r="X9" t="n">
-        <v>28.16</v>
+        <v>1085.404542648409</v>
       </c>
       <c r="Y9" t="n">
-        <v>28.16</v>
+        <v>1085.404542648409</v>
       </c>
     </row>
     <row r="10">
@@ -4929,31 +4929,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>540.0379189478641</v>
+        <v>265.1866383453244</v>
       </c>
       <c r="C10" t="n">
-        <v>672.9699247662999</v>
+        <v>398.1186441637602</v>
       </c>
       <c r="D10" t="n">
-        <v>793.2190688912999</v>
+        <v>518.3677882887603</v>
       </c>
       <c r="E10" t="n">
-        <v>917.9779731027129</v>
+        <v>643.1266925001732</v>
       </c>
       <c r="F10" t="n">
-        <v>1049.268945694648</v>
+        <v>774.4176650921088</v>
       </c>
       <c r="G10" t="n">
-        <v>1209.725123056944</v>
+        <v>934.8738424544039</v>
       </c>
       <c r="H10" t="n">
-        <v>1387.23516297044</v>
+        <v>1112.3838823679</v>
       </c>
       <c r="I10" t="n">
-        <v>1387.23516297044</v>
+        <v>1344.043804582671</v>
       </c>
       <c r="J10" t="n">
-        <v>1387.23516297044</v>
+        <v>1344.043804582671</v>
       </c>
       <c r="K10" t="n">
         <v>1387.23516297044</v>
@@ -4980,25 +4980,25 @@
         <v>28.16</v>
       </c>
       <c r="S10" t="n">
-        <v>74.42475689745181</v>
+        <v>28.16</v>
       </c>
       <c r="T10" t="n">
-        <v>74.42475689745181</v>
+        <v>28.16</v>
       </c>
       <c r="U10" t="n">
-        <v>74.42475689745181</v>
+        <v>28.16</v>
       </c>
       <c r="V10" t="n">
-        <v>74.42475689745181</v>
+        <v>28.16</v>
       </c>
       <c r="W10" t="n">
-        <v>145.0504895783462</v>
+        <v>28.16</v>
       </c>
       <c r="X10" t="n">
-        <v>303.0112806025397</v>
+        <v>28.16</v>
       </c>
       <c r="Y10" t="n">
-        <v>421.350581281572</v>
+        <v>146.4993006790323</v>
       </c>
     </row>
     <row r="11">
@@ -5011,7 +5011,7 @@
         <v>107.311807392342</v>
       </c>
       <c r="C11" t="n">
-        <v>57.33748593477238</v>
+        <v>57.33748593477237</v>
       </c>
       <c r="D11" t="n">
         <v>46.89389427835845</v>
@@ -5023,7 +5023,7 @@
         <v>37.54751214211552</v>
       </c>
       <c r="G11" t="n">
-        <v>34.02425400742071</v>
+        <v>34.02425400742069</v>
       </c>
       <c r="H11" t="n">
         <v>28.72</v>
@@ -5032,25 +5032,25 @@
         <v>28.72</v>
       </c>
       <c r="J11" t="n">
-        <v>28.72</v>
+        <v>384.1300000000135</v>
       </c>
       <c r="K11" t="n">
-        <v>62.63929542713567</v>
+        <v>418.0492954271492</v>
       </c>
       <c r="L11" t="n">
-        <v>104.7191807537688</v>
+        <v>460.1291807537824</v>
       </c>
       <c r="M11" t="n">
-        <v>331.7091164251991</v>
+        <v>815.539180753796</v>
       </c>
       <c r="N11" t="n">
-        <v>687.1191164251991</v>
+        <v>1170.94918075381</v>
       </c>
       <c r="O11" t="n">
-        <v>1042.529116425199</v>
+        <v>1170.94918075381</v>
       </c>
       <c r="P11" t="n">
-        <v>1080.59</v>
+        <v>1209.01006432861</v>
       </c>
       <c r="Q11" t="n">
         <v>1436</v>
@@ -5059,16 +5059,16 @@
         <v>1436</v>
       </c>
       <c r="S11" t="n">
-        <v>1408.846498764734</v>
+        <v>1346.393505950651</v>
       </c>
       <c r="T11" t="n">
-        <v>1221.476280176925</v>
+        <v>1159.023287362842</v>
       </c>
       <c r="U11" t="n">
-        <v>969.7593621871098</v>
+        <v>907.3063693730267</v>
       </c>
       <c r="V11" t="n">
-        <v>737.5866105034493</v>
+        <v>675.1336176893661</v>
       </c>
       <c r="W11" t="n">
         <v>496.8053216338052</v>
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>28.72</v>
+        <v>737.479694163562</v>
       </c>
       <c r="C12" t="n">
-        <v>28.72</v>
+        <v>374.8534315372855</v>
       </c>
       <c r="D12" t="n">
-        <v>28.72</v>
+        <v>374.8534315372855</v>
       </c>
       <c r="E12" t="n">
         <v>28.72</v>
@@ -5135,28 +5135,28 @@
         <v>1386.094105368536</v>
       </c>
       <c r="R12" t="n">
-        <v>1023.467842742273</v>
+        <v>1246.370734747302</v>
       </c>
       <c r="S12" t="n">
-        <v>793.7211849737801</v>
+        <v>1181.838249553394</v>
       </c>
       <c r="T12" t="n">
-        <v>788.8960457222414</v>
+        <v>1177.013110301855</v>
       </c>
       <c r="U12" t="n">
-        <v>788.6931380170785</v>
+        <v>1176.810202596692</v>
       </c>
       <c r="V12" t="n">
-        <v>774.0358984296844</v>
+        <v>1162.152963009298</v>
       </c>
       <c r="W12" t="n">
-        <v>411.4096358034217</v>
+        <v>1129.452818655936</v>
       </c>
       <c r="X12" t="n">
-        <v>391.3462626262626</v>
+        <v>1100.105956789839</v>
       </c>
       <c r="Y12" t="n">
-        <v>391.3462626262626</v>
+        <v>737.479694163562</v>
       </c>
     </row>
     <row r="13">
@@ -5166,19 +5166,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1031.971702141051</v>
+        <v>1248.108960685094</v>
       </c>
       <c r="C13" t="n">
-        <v>1157.973707959487</v>
+        <v>1374.11096650353</v>
       </c>
       <c r="D13" t="n">
-        <v>1157.973707959487</v>
+        <v>1435.860857913717</v>
       </c>
       <c r="E13" t="n">
-        <v>1157.973707959487</v>
+        <v>1435.860857913717</v>
       </c>
       <c r="F13" t="n">
-        <v>1282.334680551422</v>
+        <v>1435.860857913717</v>
       </c>
       <c r="G13" t="n">
         <v>1435.860857913717</v>
@@ -5208,7 +5208,7 @@
         <v>947.6363735028419</v>
       </c>
       <c r="P13" t="n">
-        <v>672.0451541449196</v>
+        <v>672.0451541449197</v>
       </c>
       <c r="Q13" t="n">
         <v>353.1337739170428</v>
@@ -5217,10 +5217,10 @@
         <v>28.72</v>
       </c>
       <c r="S13" t="n">
-        <v>68.05475689745181</v>
+        <v>68.05475689745182</v>
       </c>
       <c r="T13" t="n">
-        <v>256.6415032693714</v>
+        <v>256.6415032693715</v>
       </c>
       <c r="U13" t="n">
         <v>503.1992201699532</v>
@@ -5229,13 +5229,13 @@
         <v>702.020613055899</v>
       </c>
       <c r="W13" t="n">
-        <v>808.8050637957266</v>
+        <v>873.9115313155764</v>
       </c>
       <c r="X13" t="n">
-        <v>808.8050637957266</v>
+        <v>1024.94232233977</v>
       </c>
       <c r="Y13" t="n">
-        <v>920.2143644747589</v>
+        <v>1136.351623018802</v>
       </c>
     </row>
     <row r="14">
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>47.09421303037001</v>
+        <v>107.311807392342</v>
       </c>
       <c r="C14" t="n">
-        <v>47.09421303037001</v>
+        <v>57.33748593477238</v>
       </c>
       <c r="D14" t="n">
-        <v>36.65062137395608</v>
+        <v>46.89389427835845</v>
       </c>
       <c r="E14" t="n">
-        <v>32.24325813469483</v>
+        <v>42.48653103909719</v>
       </c>
       <c r="F14" t="n">
-        <v>32.24325813469483</v>
+        <v>37.54751214211552</v>
       </c>
       <c r="G14" t="n">
-        <v>28.72</v>
+        <v>34.02425400742071</v>
       </c>
       <c r="H14" t="n">
         <v>28.72</v>
@@ -5269,25 +5269,25 @@
         <v>28.72</v>
       </c>
       <c r="J14" t="n">
-        <v>28.72</v>
+        <v>384.1300000000091</v>
       </c>
       <c r="K14" t="n">
-        <v>62.63929542713567</v>
+        <v>418.0492954271447</v>
       </c>
       <c r="L14" t="n">
-        <v>418.0492954271356</v>
+        <v>687.1191164251812</v>
       </c>
       <c r="M14" t="n">
-        <v>773.4592954271357</v>
+        <v>1042.52911642519</v>
       </c>
       <c r="N14" t="n">
-        <v>1128.869295427136</v>
+        <v>1397.939116425199</v>
       </c>
       <c r="O14" t="n">
-        <v>1128.869295427136</v>
+        <v>1397.939116425199</v>
       </c>
       <c r="P14" t="n">
-        <v>1166.930179001936</v>
+        <v>1436</v>
       </c>
       <c r="Q14" t="n">
         <v>1436</v>
@@ -5299,22 +5299,22 @@
         <v>1346.393505950651</v>
       </c>
       <c r="T14" t="n">
-        <v>1159.023287362842</v>
+        <v>1221.476280176925</v>
       </c>
       <c r="U14" t="n">
-        <v>909.5417678251378</v>
+        <v>969.7593621871098</v>
       </c>
       <c r="V14" t="n">
-        <v>677.3690161414772</v>
+        <v>737.5866105034493</v>
       </c>
       <c r="W14" t="n">
-        <v>436.5877272718333</v>
+        <v>496.8053216338052</v>
       </c>
       <c r="X14" t="n">
-        <v>242.3636530691386</v>
+        <v>302.5812474311106</v>
       </c>
       <c r="Y14" t="n">
-        <v>129.9218018743847</v>
+        <v>190.1393962363566</v>
       </c>
     </row>
     <row r="15">
@@ -5324,10 +5324,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28.72</v>
+        <v>74.27417513048204</v>
       </c>
       <c r="C15" t="n">
-        <v>28.72</v>
+        <v>74.27417513048204</v>
       </c>
       <c r="D15" t="n">
         <v>28.72</v>
@@ -5375,25 +5375,25 @@
         <v>1246.370734747302</v>
       </c>
       <c r="S15" t="n">
-        <v>1181.838249553394</v>
+        <v>1181.838249553393</v>
       </c>
       <c r="T15" t="n">
         <v>1177.013110301855</v>
       </c>
       <c r="U15" t="n">
-        <v>814.3868476755924</v>
+        <v>1176.810202596692</v>
       </c>
       <c r="V15" t="n">
-        <v>799.7296080881983</v>
+        <v>1162.152963009298</v>
       </c>
       <c r="W15" t="n">
-        <v>753.9725252525252</v>
+        <v>799.5267003830259</v>
       </c>
       <c r="X15" t="n">
-        <v>391.3462626262626</v>
+        <v>436.9004377567539</v>
       </c>
       <c r="Y15" t="n">
-        <v>28.72</v>
+        <v>436.9004377567539</v>
       </c>
     </row>
     <row r="16">
@@ -5403,31 +5403,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1248.108960685094</v>
+        <v>1080.451696951911</v>
       </c>
       <c r="C16" t="n">
-        <v>1248.108960685094</v>
+        <v>1080.451696951911</v>
       </c>
       <c r="D16" t="n">
-        <v>1311.499885321782</v>
+        <v>1193.770841076911</v>
       </c>
       <c r="E16" t="n">
-        <v>1311.499885321782</v>
+        <v>1311.599745288324</v>
       </c>
       <c r="F16" t="n">
-        <v>1435.860857913717</v>
+        <v>1311.599745288324</v>
       </c>
       <c r="G16" t="n">
-        <v>1435.860857913717</v>
+        <v>1311.599745288324</v>
       </c>
       <c r="H16" t="n">
-        <v>1435.860857913717</v>
+        <v>1311.599745288324</v>
       </c>
       <c r="I16" t="n">
-        <v>1435.860857913717</v>
+        <v>1311.599745288324</v>
       </c>
       <c r="J16" t="n">
-        <v>1435.860857913717</v>
+        <v>1311.599745288324</v>
       </c>
       <c r="K16" t="n">
         <v>1435.860857913717</v>
@@ -5445,7 +5445,7 @@
         <v>947.6363735028419</v>
       </c>
       <c r="P16" t="n">
-        <v>672.0451541449197</v>
+        <v>672.0451541449196</v>
       </c>
       <c r="Q16" t="n">
         <v>353.1337739170428</v>
@@ -5454,25 +5454,25 @@
         <v>28.72</v>
       </c>
       <c r="S16" t="n">
-        <v>68.05475689745182</v>
+        <v>28.72</v>
       </c>
       <c r="T16" t="n">
-        <v>256.6415032693715</v>
+        <v>217.3067463719196</v>
       </c>
       <c r="U16" t="n">
-        <v>503.1992201699532</v>
+        <v>463.8644632725013</v>
       </c>
       <c r="V16" t="n">
-        <v>702.020613055899</v>
+        <v>662.6858561584472</v>
       </c>
       <c r="W16" t="n">
-        <v>873.9115313155764</v>
+        <v>834.5767744181246</v>
       </c>
       <c r="X16" t="n">
-        <v>1024.94232233977</v>
+        <v>985.6075654423181</v>
       </c>
       <c r="Y16" t="n">
-        <v>1136.351623018802</v>
+        <v>1080.451696951911</v>
       </c>
     </row>
     <row r="17">
@@ -5482,22 +5482,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>81.42406423203268</v>
+        <v>82.3226790886103</v>
       </c>
       <c r="C17" t="n">
-        <v>35.4901468148671</v>
+        <v>36.38876167144473</v>
       </c>
       <c r="D17" t="n">
-        <v>29.08695919885722</v>
+        <v>29.98557405543485</v>
       </c>
       <c r="E17" t="n">
-        <v>28.72</v>
+        <v>29.61861485657763</v>
       </c>
       <c r="F17" t="n">
         <v>28.72</v>
       </c>
       <c r="G17" t="n">
-        <v>29.22685470218561</v>
+        <v>29.22685470218989</v>
       </c>
       <c r="H17" t="n">
         <v>28.72</v>
@@ -5509,22 +5509,22 @@
         <v>28.72</v>
       </c>
       <c r="K17" t="n">
-        <v>384.13</v>
+        <v>62.63929542713567</v>
       </c>
       <c r="L17" t="n">
-        <v>426.2098853266332</v>
+        <v>331.7091164251717</v>
       </c>
       <c r="M17" t="n">
-        <v>781.6198853266333</v>
+        <v>687.1191164251809</v>
       </c>
       <c r="N17" t="n">
-        <v>1042.529116425199</v>
+        <v>1042.52911642519</v>
       </c>
       <c r="O17" t="n">
-        <v>1042.529116425199</v>
+        <v>1042.52911642519</v>
       </c>
       <c r="P17" t="n">
-        <v>1080.59</v>
+        <v>1080.589999999991</v>
       </c>
       <c r="Q17" t="n">
         <v>1436</v>
@@ -5536,22 +5536,22 @@
         <v>1350.433909991055</v>
       </c>
       <c r="T17" t="n">
-        <v>1171.346112774192</v>
+        <v>1167.10409544365</v>
       </c>
       <c r="U17" t="n">
-        <v>923.6695988247802</v>
+        <v>924.568213681358</v>
       </c>
       <c r="V17" t="n">
-        <v>695.5372511815237</v>
+        <v>696.4358660381015</v>
       </c>
       <c r="W17" t="n">
-        <v>458.7963663522838</v>
+        <v>459.6949812088615</v>
       </c>
       <c r="X17" t="n">
-        <v>268.6126961899932</v>
+        <v>269.5113110465708</v>
       </c>
       <c r="Y17" t="n">
-        <v>160.2112490356433</v>
+        <v>161.1098638922209</v>
       </c>
     </row>
     <row r="18">
@@ -5609,28 +5609,28 @@
         <v>1386.094105368536</v>
       </c>
       <c r="R18" t="n">
-        <v>1023.467842742273</v>
+        <v>1250.411138787706</v>
       </c>
       <c r="S18" t="n">
-        <v>962.9757615887681</v>
+        <v>1156.660098949899</v>
       </c>
       <c r="T18" t="n">
-        <v>962.1910263776335</v>
+        <v>1155.875363738764</v>
       </c>
       <c r="U18" t="n">
-        <v>962.1910263776335</v>
+        <v>1155.875363738764</v>
       </c>
       <c r="V18" t="n">
-        <v>782.6322655654833</v>
+        <v>1145.258528191774</v>
       </c>
       <c r="W18" t="n">
-        <v>753.9725252525252</v>
+        <v>1116.598787878816</v>
       </c>
       <c r="X18" t="n">
-        <v>391.3462626262626</v>
+        <v>753.9725252525441</v>
       </c>
       <c r="Y18" t="n">
-        <v>28.72</v>
+        <v>391.3462626262721</v>
       </c>
     </row>
     <row r="19">
@@ -5640,25 +5640,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>846.8618901403265</v>
+        <v>790.2831938247394</v>
       </c>
       <c r="C19" t="n">
-        <v>846.8618901403265</v>
+        <v>920.2451996431753</v>
       </c>
       <c r="D19" t="n">
-        <v>846.8618901403265</v>
+        <v>1037.524343768175</v>
       </c>
       <c r="E19" t="n">
-        <v>846.8618901403265</v>
+        <v>1159.313247979588</v>
       </c>
       <c r="F19" t="n">
-        <v>846.8618901403265</v>
+        <v>1287.634220571524</v>
       </c>
       <c r="G19" t="n">
-        <v>1004.348067502622</v>
+        <v>1407.578029630889</v>
       </c>
       <c r="H19" t="n">
-        <v>1178.888107416117</v>
+        <v>1407.578029630889</v>
       </c>
       <c r="I19" t="n">
         <v>1407.578029630889</v>
@@ -5691,25 +5691,25 @@
         <v>28.72</v>
       </c>
       <c r="S19" t="n">
-        <v>72.0147568974518</v>
+        <v>28.72</v>
       </c>
       <c r="T19" t="n">
-        <v>72.0147568974518</v>
+        <v>221.2667463719196</v>
       </c>
       <c r="U19" t="n">
-        <v>322.5324737980335</v>
+        <v>471.7844632725013</v>
       </c>
       <c r="V19" t="n">
-        <v>322.5324737980335</v>
+        <v>674.5658561584473</v>
       </c>
       <c r="W19" t="n">
-        <v>460.7844607708087</v>
+        <v>674.5658561584473</v>
       </c>
       <c r="X19" t="n">
-        <v>615.7752517950022</v>
+        <v>674.5658561584473</v>
       </c>
       <c r="Y19" t="n">
-        <v>731.1445524740344</v>
+        <v>674.5658561584473</v>
       </c>
     </row>
     <row r="20">
@@ -5719,22 +5719,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>83.07967435343394</v>
+        <v>83.0796743534346</v>
       </c>
       <c r="C20" t="n">
-        <v>37.14575693626837</v>
+        <v>37.14575693626902</v>
       </c>
       <c r="D20" t="n">
-        <v>30.74256932025848</v>
+        <v>30.74256932025913</v>
       </c>
       <c r="E20" t="n">
-        <v>30.37561012140126</v>
+        <v>30.37561012140191</v>
       </c>
       <c r="F20" t="n">
-        <v>29.47699526482363</v>
+        <v>29.47699526482428</v>
       </c>
       <c r="G20" t="n">
-        <v>29.98384996701667</v>
+        <v>29.98384996701665</v>
       </c>
       <c r="H20" t="n">
         <v>28.72</v>
@@ -5743,25 +5743,25 @@
         <v>28.72</v>
       </c>
       <c r="J20" t="n">
-        <v>28.72</v>
+        <v>384.1300000000092</v>
       </c>
       <c r="K20" t="n">
-        <v>62.63929542713567</v>
+        <v>739.5400000000091</v>
       </c>
       <c r="L20" t="n">
-        <v>104.7191807537688</v>
+        <v>781.6198853266422</v>
       </c>
       <c r="M20" t="n">
-        <v>460.1291807537689</v>
+        <v>1042.52911642519</v>
       </c>
       <c r="N20" t="n">
-        <v>815.539180753769</v>
+        <v>1042.52911642519</v>
       </c>
       <c r="O20" t="n">
-        <v>1170.949180753769</v>
+        <v>1042.52911642519</v>
       </c>
       <c r="P20" t="n">
-        <v>1209.01006432857</v>
+        <v>1080.589999999991</v>
       </c>
       <c r="Q20" t="n">
         <v>1436</v>
@@ -5773,22 +5773,22 @@
         <v>1356.331537442998</v>
       </c>
       <c r="T20" t="n">
-        <v>1173.001722895593</v>
+        <v>1173.001722895594</v>
       </c>
       <c r="U20" t="n">
-        <v>925.3252089461815</v>
+        <v>925.3252089461822</v>
       </c>
       <c r="V20" t="n">
-        <v>697.1928613029251</v>
+        <v>697.1928613029257</v>
       </c>
       <c r="W20" t="n">
-        <v>460.4519764736851</v>
+        <v>460.4519764736858</v>
       </c>
       <c r="X20" t="n">
-        <v>270.2683063113944</v>
+        <v>270.2683063113951</v>
       </c>
       <c r="Y20" t="n">
-        <v>161.8668591570446</v>
+        <v>161.8668591570452</v>
       </c>
     </row>
     <row r="21">
@@ -5798,25 +5798,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>243.0276701399175</v>
+        <v>1085.865383066252</v>
       </c>
       <c r="C21" t="n">
-        <v>243.0276701399175</v>
+        <v>723.2391204399794</v>
       </c>
       <c r="D21" t="n">
-        <v>243.0276701399175</v>
+        <v>371.7869114524009</v>
       </c>
       <c r="E21" t="n">
-        <v>243.0276701399175</v>
+        <v>371.7869114524009</v>
       </c>
       <c r="F21" t="n">
-        <v>243.0276701399175</v>
+        <v>28.72</v>
       </c>
       <c r="G21" t="n">
-        <v>243.0276701399175</v>
+        <v>28.72</v>
       </c>
       <c r="H21" t="n">
-        <v>243.0276701399175</v>
+        <v>28.72</v>
       </c>
       <c r="I21" t="n">
         <v>28.72</v>
@@ -5843,31 +5843,31 @@
         <v>1386.094105368536</v>
       </c>
       <c r="Q21" t="n">
-        <v>1229.848306820881</v>
+        <v>1386.094105368536</v>
       </c>
       <c r="R21" t="n">
-        <v>867.2220441946188</v>
+        <v>1202.441744427594</v>
       </c>
       <c r="S21" t="n">
-        <v>504.5957815683561</v>
+        <v>1141.94966327409</v>
       </c>
       <c r="T21" t="n">
-        <v>298.3272151366208</v>
+        <v>1141.164928062955</v>
       </c>
       <c r="U21" t="n">
-        <v>298.3272151366208</v>
+        <v>1141.164928062955</v>
       </c>
       <c r="V21" t="n">
-        <v>287.7103795896307</v>
+        <v>1130.548092515965</v>
       </c>
       <c r="W21" t="n">
-        <v>259.0506392766727</v>
+        <v>1101.888352203007</v>
       </c>
       <c r="X21" t="n">
-        <v>243.0276701399175</v>
+        <v>1085.865383066252</v>
       </c>
       <c r="Y21" t="n">
-        <v>243.0276701399175</v>
+        <v>1085.865383066252</v>
       </c>
     </row>
     <row r="22">
@@ -5877,19 +5877,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1002.850702325158</v>
+        <v>1043.947457415723</v>
       </c>
       <c r="C22" t="n">
-        <v>1132.812708143594</v>
+        <v>1173.909463234159</v>
       </c>
       <c r="D22" t="n">
-        <v>1250.091852268594</v>
+        <v>1291.188607359159</v>
       </c>
       <c r="E22" t="n">
-        <v>1250.091852268594</v>
+        <v>1407.578029630889</v>
       </c>
       <c r="F22" t="n">
-        <v>1250.091852268594</v>
+        <v>1407.578029630889</v>
       </c>
       <c r="G22" t="n">
         <v>1407.578029630889</v>
@@ -5916,10 +5916,10 @@
         <v>1157.099254920625</v>
       </c>
       <c r="O22" t="n">
-        <v>935.5151613816297</v>
+        <v>935.5151613816299</v>
       </c>
       <c r="P22" t="n">
-        <v>663.9643460641115</v>
+        <v>663.9643460641116</v>
       </c>
       <c r="Q22" t="n">
         <v>349.0933698766388</v>
@@ -5931,22 +5931,22 @@
         <v>28.72</v>
       </c>
       <c r="T22" t="n">
-        <v>221.2667463719196</v>
+        <v>28.72</v>
       </c>
       <c r="U22" t="n">
-        <v>471.7844632725013</v>
+        <v>279.2377169005817</v>
       </c>
       <c r="V22" t="n">
-        <v>674.5658561584473</v>
+        <v>482.0191097865277</v>
       </c>
       <c r="W22" t="n">
-        <v>732.4906106219322</v>
+        <v>657.8700280462051</v>
       </c>
       <c r="X22" t="n">
-        <v>887.4814016461257</v>
+        <v>812.8608190703986</v>
       </c>
       <c r="Y22" t="n">
-        <v>1002.850702325158</v>
+        <v>928.2301197494309</v>
       </c>
     </row>
     <row r="23">
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>83.07967435343527</v>
+        <v>82.3226790886103</v>
       </c>
       <c r="C23" t="n">
-        <v>37.14575693626969</v>
+        <v>36.38876167144473</v>
       </c>
       <c r="D23" t="n">
-        <v>30.74256932025981</v>
+        <v>29.98557405543485</v>
       </c>
       <c r="E23" t="n">
-        <v>30.37561012140259</v>
+        <v>29.61861485657763</v>
       </c>
       <c r="F23" t="n">
-        <v>29.47699526482496</v>
+        <v>28.72</v>
       </c>
       <c r="G23" t="n">
-        <v>29.98384996701665</v>
+        <v>29.22685470218561</v>
       </c>
       <c r="H23" t="n">
         <v>28.72</v>
@@ -5983,22 +5983,22 @@
         <v>28.72</v>
       </c>
       <c r="K23" t="n">
-        <v>384.13</v>
+        <v>62.63929542713567</v>
       </c>
       <c r="L23" t="n">
-        <v>687.1191164251991</v>
+        <v>418.0492954271356</v>
       </c>
       <c r="M23" t="n">
-        <v>1042.529116425199</v>
+        <v>773.459295427146</v>
       </c>
       <c r="N23" t="n">
-        <v>1397.939116425199</v>
+        <v>1042.529116425189</v>
       </c>
       <c r="O23" t="n">
-        <v>1397.939116425199</v>
+        <v>1042.529116425189</v>
       </c>
       <c r="P23" t="n">
-        <v>1436</v>
+        <v>1080.58999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>1436</v>
@@ -6007,25 +6007,25 @@
         <v>1436</v>
       </c>
       <c r="S23" t="n">
-        <v>1356.331537442999</v>
+        <v>1350.433909991055</v>
       </c>
       <c r="T23" t="n">
-        <v>1173.001722895594</v>
+        <v>1167.10409544365</v>
       </c>
       <c r="U23" t="n">
-        <v>925.3252089461829</v>
+        <v>919.4275814942388</v>
       </c>
       <c r="V23" t="n">
-        <v>697.1928613029264</v>
+        <v>691.2952338509823</v>
       </c>
       <c r="W23" t="n">
-        <v>460.4519764736864</v>
+        <v>459.6949812088615</v>
       </c>
       <c r="X23" t="n">
-        <v>270.2683063113958</v>
+        <v>269.5113110465708</v>
       </c>
       <c r="Y23" t="n">
-        <v>161.8668591570459</v>
+        <v>161.1098638922209</v>
       </c>
     </row>
     <row r="24">
@@ -6035,16 +6035,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>28.72</v>
+        <v>1133.834777426364</v>
       </c>
       <c r="C24" t="n">
-        <v>28.72</v>
+        <v>1069.372551977265</v>
       </c>
       <c r="D24" t="n">
-        <v>28.72</v>
+        <v>717.9203429896863</v>
       </c>
       <c r="E24" t="n">
-        <v>28.72</v>
+        <v>371.7869114524009</v>
       </c>
       <c r="F24" t="n">
         <v>28.72</v>
@@ -6086,25 +6086,25 @@
         <v>1250.411138787706</v>
       </c>
       <c r="S24" t="n">
-        <v>1133.406492226678</v>
+        <v>1189.919057634202</v>
       </c>
       <c r="T24" t="n">
-        <v>1132.621757015543</v>
+        <v>1189.134322423067</v>
       </c>
       <c r="U24" t="n">
-        <v>769.9954943892803</v>
+        <v>1189.134322423067</v>
       </c>
       <c r="V24" t="n">
-        <v>407.3692317630178</v>
+        <v>1178.517486876077</v>
       </c>
       <c r="W24" t="n">
-        <v>44.74296913675509</v>
+        <v>1149.857746563119</v>
       </c>
       <c r="X24" t="n">
-        <v>28.72</v>
+        <v>1133.834777426364</v>
       </c>
       <c r="Y24" t="n">
-        <v>28.72</v>
+        <v>1133.834777426364</v>
       </c>
     </row>
     <row r="25">
@@ -6114,28 +6114,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>777.4027081435938</v>
+        <v>717.8606130558991</v>
       </c>
       <c r="C25" t="n">
-        <v>777.4027081435938</v>
+        <v>717.8606130558991</v>
       </c>
       <c r="D25" t="n">
-        <v>894.681852268594</v>
+        <v>835.1397571808991</v>
       </c>
       <c r="E25" t="n">
-        <v>894.681852268594</v>
+        <v>835.1397571808991</v>
       </c>
       <c r="F25" t="n">
-        <v>894.681852268594</v>
+        <v>963.4607297728346</v>
       </c>
       <c r="G25" t="n">
-        <v>1052.168029630889</v>
+        <v>1120.94690713513</v>
       </c>
       <c r="H25" t="n">
-        <v>1052.168029630889</v>
+        <v>1295.486947048626</v>
       </c>
       <c r="I25" t="n">
-        <v>1052.168029630889</v>
+        <v>1407.578029630889</v>
       </c>
       <c r="J25" t="n">
         <v>1407.578029630889</v>
@@ -6153,10 +6153,10 @@
         <v>1157.099254920625</v>
       </c>
       <c r="O25" t="n">
-        <v>935.5151613816299</v>
+        <v>935.5151613816297</v>
       </c>
       <c r="P25" t="n">
-        <v>663.9643460641116</v>
+        <v>663.9643460641115</v>
       </c>
       <c r="Q25" t="n">
         <v>349.0933698766388</v>
@@ -6165,25 +6165,25 @@
         <v>28.72</v>
       </c>
       <c r="S25" t="n">
-        <v>28.72</v>
+        <v>72.0147568974518</v>
       </c>
       <c r="T25" t="n">
-        <v>215.4743605143986</v>
+        <v>264.5615032693714</v>
       </c>
       <c r="U25" t="n">
-        <v>215.4743605143986</v>
+        <v>515.0792201699531</v>
       </c>
       <c r="V25" t="n">
-        <v>215.4743605143986</v>
+        <v>717.8606130558991</v>
       </c>
       <c r="W25" t="n">
-        <v>391.325278774076</v>
+        <v>717.8606130558991</v>
       </c>
       <c r="X25" t="n">
-        <v>546.3160697982695</v>
+        <v>717.8606130558991</v>
       </c>
       <c r="Y25" t="n">
-        <v>661.6853704773017</v>
+        <v>717.8606130558991</v>
       </c>
     </row>
     <row r="26">
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>323.5097756071435</v>
+        <v>373.2584740590087</v>
       </c>
       <c r="C26" t="n">
-        <v>229.0910097051295</v>
+        <v>278.8397081569946</v>
       </c>
       <c r="D26" t="n">
-        <v>174.2029736042711</v>
+        <v>223.9516720561363</v>
       </c>
       <c r="E26" t="n">
-        <v>125.3511659205654</v>
+        <v>175.0998643724305</v>
       </c>
       <c r="F26" t="n">
-        <v>75.96770257913929</v>
+        <v>125.7164010310044</v>
       </c>
       <c r="G26" t="n">
-        <v>28</v>
+        <v>77.74869845186512</v>
       </c>
       <c r="H26" t="n">
         <v>28</v>
@@ -6217,25 +6217,25 @@
         <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>28</v>
+        <v>374.5000000000231</v>
       </c>
       <c r="K26" t="n">
-        <v>61.91929542713567</v>
+        <v>664.9201146733204</v>
       </c>
       <c r="L26" t="n">
-        <v>103.9991807537688</v>
+        <v>706.9999999999536</v>
       </c>
       <c r="M26" t="n">
-        <v>450.4991807537688</v>
+        <v>706.9999999999536</v>
       </c>
       <c r="N26" t="n">
-        <v>668.9391164251992</v>
+        <v>706.9999999999536</v>
       </c>
       <c r="O26" t="n">
-        <v>1015.439116425199</v>
+        <v>706.9999999999536</v>
       </c>
       <c r="P26" t="n">
-        <v>1053.5</v>
+        <v>1053.499999999977</v>
       </c>
       <c r="Q26" t="n">
         <v>1400</v>
@@ -6250,19 +6250,19 @@
         <v>1168.185336967747</v>
       </c>
       <c r="U26" t="n">
-        <v>872.0239745334869</v>
+        <v>1168.185336967747</v>
       </c>
       <c r="V26" t="n">
-        <v>595.4067784053819</v>
+        <v>1168.185336967747</v>
       </c>
       <c r="W26" t="n">
-        <v>480.3960712463419</v>
+        <v>896.0853216338053</v>
       </c>
       <c r="X26" t="n">
-        <v>480.3960712463419</v>
+        <v>657.4168029866662</v>
       </c>
       <c r="Y26" t="n">
-        <v>323.5097756071435</v>
+        <v>500.5305073474678</v>
       </c>
     </row>
     <row r="27">
@@ -6272,7 +6272,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>33.15142671264575</v>
+        <v>381.5353535353772</v>
       </c>
       <c r="C27" t="n">
         <v>28</v>
@@ -6323,25 +6323,25 @@
         <v>1201.206290302858</v>
       </c>
       <c r="S27" t="n">
-        <v>847.6709367675044</v>
+        <v>1053.146846047834</v>
       </c>
       <c r="T27" t="n">
-        <v>494.1355832321508</v>
+        <v>699.6114925124565</v>
       </c>
       <c r="U27" t="n">
-        <v>306.5802135401177</v>
+        <v>654.9641403628491</v>
       </c>
       <c r="V27" t="n">
-        <v>247.4785295082791</v>
+        <v>595.8624563310105</v>
       </c>
       <c r="W27" t="n">
-        <v>170.3339407104725</v>
+        <v>518.717867533204</v>
       </c>
       <c r="X27" t="n">
-        <v>105.8261230888689</v>
+        <v>454.2100499116003</v>
       </c>
       <c r="Y27" t="n">
-        <v>61.99643342610698</v>
+        <v>410.3803602488384</v>
       </c>
     </row>
     <row r="28">
@@ -6351,25 +6351,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>835.2849031086104</v>
+        <v>903.1342037876426</v>
       </c>
       <c r="C28" t="n">
-        <v>917.7269089270461</v>
+        <v>903.1342037876426</v>
       </c>
       <c r="D28" t="n">
-        <v>987.4860530520461</v>
+        <v>972.8933479126426</v>
       </c>
       <c r="E28" t="n">
-        <v>1061.754957263459</v>
+        <v>1011.009065279797</v>
       </c>
       <c r="F28" t="n">
-        <v>1142.555929855395</v>
+        <v>1091.810037871732</v>
       </c>
       <c r="G28" t="n">
-        <v>1252.52210721769</v>
+        <v>1091.810037871732</v>
       </c>
       <c r="H28" t="n">
-        <v>1379.542147131186</v>
+        <v>1218.830077785228</v>
       </c>
       <c r="I28" t="n">
         <v>1400</v>
@@ -6387,16 +6387,16 @@
         <v>1252.835779176096</v>
       </c>
       <c r="N28" t="n">
-        <v>1252.835779176096</v>
+        <v>1054.15257679867</v>
       </c>
       <c r="O28" t="n">
-        <v>1059.417403525403</v>
+        <v>784.0836347748264</v>
       </c>
       <c r="P28" t="n">
-        <v>739.3817397230366</v>
+        <v>739.3817397230839</v>
       </c>
       <c r="Q28" t="n">
-        <v>385.8463861876831</v>
+        <v>385.8463861877067</v>
       </c>
       <c r="R28" t="n">
         <v>32.31103265232954</v>
@@ -6420,7 +6420,7 @@
         <v>767.0875654423182</v>
       </c>
       <c r="Y28" t="n">
-        <v>767.0875654423182</v>
+        <v>834.9368661213505</v>
       </c>
     </row>
     <row r="29">
@@ -6430,19 +6430,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>293.5719804145522</v>
+        <v>115.0109496720791</v>
       </c>
       <c r="C29" t="n">
-        <v>205.2138205731442</v>
+        <v>115.0109496720791</v>
       </c>
       <c r="D29" t="n">
-        <v>156.3863905328919</v>
+        <v>115.0109496720791</v>
       </c>
       <c r="E29" t="n">
-        <v>113.5951889097923</v>
+        <v>115.0109496720791</v>
       </c>
       <c r="F29" t="n">
-        <v>113.5951889097923</v>
+        <v>71.68809239125909</v>
       </c>
       <c r="G29" t="n">
         <v>71.68809239125909</v>
@@ -6457,22 +6457,22 @@
         <v>28</v>
       </c>
       <c r="K29" t="n">
-        <v>61.91929542713567</v>
+        <v>280.3592310985142</v>
       </c>
       <c r="L29" t="n">
-        <v>103.9991807537688</v>
+        <v>322.4391164251474</v>
       </c>
       <c r="M29" t="n">
-        <v>450.4991807537688</v>
+        <v>668.9391164251647</v>
       </c>
       <c r="N29" t="n">
-        <v>707</v>
+        <v>1015.439116425182</v>
       </c>
       <c r="O29" t="n">
-        <v>1053.5</v>
+        <v>1015.439116425182</v>
       </c>
       <c r="P29" t="n">
-        <v>1400</v>
+        <v>1053.499999999983</v>
       </c>
       <c r="Q29" t="n">
         <v>1400</v>
@@ -6484,22 +6484,22 @@
         <v>1400</v>
       </c>
       <c r="T29" t="n">
-        <v>1174.245943028353</v>
+        <v>1338.267025531839</v>
       </c>
       <c r="U29" t="n">
-        <v>884.1451866546989</v>
+        <v>1048.166269158186</v>
       </c>
       <c r="V29" t="n">
-        <v>613.5885965872001</v>
+        <v>777.6096790906869</v>
       </c>
       <c r="W29" t="n">
-        <v>334.4234693337177</v>
+        <v>498.4445518372045</v>
       </c>
       <c r="X29" t="n">
-        <v>293.5719804145522</v>
+        <v>265.8366392506715</v>
       </c>
       <c r="Y29" t="n">
-        <v>293.5719804145522</v>
+        <v>115.0109496720791</v>
       </c>
     </row>
     <row r="30">
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>242.3076701399175</v>
+        <v>779.4290925368966</v>
       </c>
       <c r="C30" t="n">
-        <v>242.3076701399175</v>
+        <v>576.4251014507679</v>
       </c>
       <c r="D30" t="n">
-        <v>242.3076701399175</v>
+        <v>576.4251014507679</v>
       </c>
       <c r="E30" t="n">
-        <v>242.3076701399175</v>
+        <v>576.4251014507679</v>
       </c>
       <c r="F30" t="n">
-        <v>242.3076701399175</v>
+        <v>576.4251014507679</v>
       </c>
       <c r="G30" t="n">
-        <v>242.3076701399175</v>
+        <v>576.4251014507679</v>
       </c>
       <c r="H30" t="n">
         <v>242.3076701399175</v>
@@ -6557,28 +6557,28 @@
         <v>1385.374105368536</v>
       </c>
       <c r="R30" t="n">
-        <v>1031.838751833182</v>
+        <v>1207.266896363464</v>
       </c>
       <c r="S30" t="n">
-        <v>928.9224282554347</v>
+        <v>1104.350572785717</v>
       </c>
       <c r="T30" t="n">
-        <v>575.3870747200812</v>
+        <v>1061.14159515034</v>
       </c>
       <c r="U30" t="n">
-        <v>536.8003286310799</v>
+        <v>1022.554849061338</v>
       </c>
       <c r="V30" t="n">
-        <v>432.3923486931266</v>
+        <v>969.5137710901058</v>
       </c>
       <c r="W30" t="n">
-        <v>361.3083659559261</v>
+        <v>898.4297883529052</v>
       </c>
       <c r="X30" t="n">
-        <v>302.8611543949286</v>
+        <v>839.9825767919077</v>
       </c>
       <c r="Y30" t="n">
-        <v>265.0920707927727</v>
+        <v>802.2134931897518</v>
       </c>
     </row>
     <row r="31">
@@ -6588,31 +6588,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>664.2314040800926</v>
+        <v>946.4289606850944</v>
       </c>
       <c r="C31" t="n">
-        <v>664.2314040800926</v>
+        <v>946.4289606850944</v>
       </c>
       <c r="D31" t="n">
-        <v>664.2314040800926</v>
+        <v>1022.128104810094</v>
       </c>
       <c r="E31" t="n">
-        <v>664.2314040800926</v>
+        <v>1022.128104810094</v>
       </c>
       <c r="F31" t="n">
-        <v>664.2314040800926</v>
+        <v>1108.86907740203</v>
       </c>
       <c r="G31" t="n">
-        <v>780.1375814423877</v>
+        <v>1224.775254764325</v>
       </c>
       <c r="H31" t="n">
-        <v>913.0976213558836</v>
+        <v>1224.775254764325</v>
       </c>
       <c r="I31" t="n">
-        <v>1100.207543570655</v>
+        <v>1224.775254764325</v>
       </c>
       <c r="J31" t="n">
-        <v>1400</v>
+        <v>1313.358887374607</v>
       </c>
       <c r="K31" t="n">
         <v>1400</v>
@@ -6621,19 +6621,19 @@
         <v>1400</v>
       </c>
       <c r="M31" t="n">
-        <v>1400</v>
+        <v>1258.896385236702</v>
       </c>
       <c r="N31" t="n">
-        <v>1313.054100775705</v>
+        <v>1066.273788919882</v>
       </c>
       <c r="O31" t="n">
-        <v>1049.045764812468</v>
+        <v>802.2654529566445</v>
       </c>
       <c r="P31" t="n">
-        <v>735.0707070707072</v>
+        <v>488.2903952148839</v>
       </c>
       <c r="Q31" t="n">
-        <v>381.5353535353536</v>
+        <v>381.5353535353712</v>
       </c>
       <c r="R31" t="n">
         <v>28</v>
@@ -6651,13 +6651,13 @@
         <v>550.8206130558991</v>
       </c>
       <c r="W31" t="n">
-        <v>550.8206130558991</v>
+        <v>685.0915313155765</v>
       </c>
       <c r="X31" t="n">
-        <v>664.2314040800926</v>
+        <v>798.50232233977</v>
       </c>
       <c r="Y31" t="n">
-        <v>664.2314040800926</v>
+        <v>872.2916230188023</v>
       </c>
     </row>
     <row r="32">
@@ -6691,19 +6691,19 @@
         <v>27.52</v>
       </c>
       <c r="J32" t="n">
-        <v>368.08</v>
+        <v>27.52</v>
       </c>
       <c r="K32" t="n">
-        <v>401.9992954271357</v>
+        <v>61.43929542713568</v>
       </c>
       <c r="L32" t="n">
-        <v>444.0791807537688</v>
+        <v>316.2591164251994</v>
       </c>
       <c r="M32" t="n">
-        <v>444.0791807537689</v>
+        <v>656.8191164251994</v>
       </c>
       <c r="N32" t="n">
-        <v>656.8191164251994</v>
+        <v>997.3791164251993</v>
       </c>
       <c r="O32" t="n">
         <v>997.3791164251993</v>
@@ -6724,19 +6724,19 @@
         <v>1119.225307564862</v>
       </c>
       <c r="U32" t="n">
-        <v>879.6783972016806</v>
+        <v>877.609399676057</v>
       </c>
       <c r="V32" t="n">
-        <v>657.6066556190302</v>
+        <v>655.5376580934067</v>
       </c>
       <c r="W32" t="n">
-        <v>426.9263768503963</v>
+        <v>424.8573793247728</v>
       </c>
       <c r="X32" t="n">
-        <v>242.8033127487117</v>
+        <v>240.7343152230882</v>
       </c>
       <c r="Y32" t="n">
-        <v>140.4624716549679</v>
+        <v>138.3934741293443</v>
       </c>
     </row>
     <row r="33">
@@ -6746,22 +6746,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>361.6374313108504</v>
+        <v>27.52</v>
       </c>
       <c r="C33" t="n">
-        <v>361.6374313108504</v>
+        <v>27.52</v>
       </c>
       <c r="D33" t="n">
-        <v>361.6374313108504</v>
+        <v>27.52</v>
       </c>
       <c r="E33" t="n">
-        <v>361.6374313108504</v>
+        <v>27.52</v>
       </c>
       <c r="F33" t="n">
-        <v>361.6374313108504</v>
+        <v>27.52</v>
       </c>
       <c r="G33" t="n">
-        <v>361.6374313108504</v>
+        <v>27.52</v>
       </c>
       <c r="H33" t="n">
         <v>27.52</v>
@@ -6776,13 +6776,13 @@
         <v>377.1871300432672</v>
       </c>
       <c r="L33" t="n">
-        <v>670.6214735340828</v>
+        <v>679.5155789026182</v>
       </c>
       <c r="M33" t="n">
-        <v>792.851865276942</v>
+        <v>801.7459706454774</v>
       </c>
       <c r="N33" t="n">
-        <v>963.2387788467745</v>
+        <v>972.1328842153099</v>
       </c>
       <c r="O33" t="n">
         <v>1236.226546662569</v>
@@ -6794,28 +6794,28 @@
         <v>1219.754201452346</v>
       </c>
       <c r="R33" t="n">
-        <v>872.2794539775982</v>
+        <v>1090.131840932123</v>
       </c>
       <c r="S33" t="n">
-        <v>817.8479788846994</v>
+        <v>1035.700365839224</v>
       </c>
       <c r="T33" t="n">
-        <v>470.3732314099519</v>
+        <v>1035.700365839224</v>
       </c>
       <c r="U33" t="n">
-        <v>470.3732314099519</v>
+        <v>688.2256183644763</v>
       </c>
       <c r="V33" t="n">
-        <v>465.8170019235679</v>
+        <v>340.7508708897288</v>
       </c>
       <c r="W33" t="n">
-        <v>371.5997943869994</v>
+        <v>37.48236307614903</v>
       </c>
       <c r="X33" t="n">
-        <v>361.6374313108504</v>
+        <v>27.52</v>
       </c>
       <c r="Y33" t="n">
-        <v>361.6374313108504</v>
+        <v>27.52</v>
       </c>
     </row>
     <row r="34">
@@ -6825,34 +6825,34 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>777.4498485417364</v>
+        <v>1078.387457415723</v>
       </c>
       <c r="C34" t="n">
-        <v>777.4498485417364</v>
+        <v>1214.289463234159</v>
       </c>
       <c r="D34" t="n">
-        <v>777.4498485417364</v>
+        <v>1337.508607359159</v>
       </c>
       <c r="E34" t="n">
-        <v>777.4498485417364</v>
+        <v>1337.508607359159</v>
       </c>
       <c r="F34" t="n">
-        <v>777.4498485417364</v>
+        <v>1337.508607359159</v>
       </c>
       <c r="G34" t="n">
-        <v>777.4498485417364</v>
+        <v>1337.508607359159</v>
       </c>
       <c r="H34" t="n">
-        <v>957.9298884552323</v>
+        <v>1337.508607359159</v>
       </c>
       <c r="I34" t="n">
-        <v>957.9298884552323</v>
+        <v>1364.042532402528</v>
       </c>
       <c r="J34" t="n">
-        <v>1298.489888455232</v>
+        <v>1364.042532402528</v>
       </c>
       <c r="K34" t="n">
-        <v>1368.413344788622</v>
+        <v>1364.042532402528</v>
       </c>
       <c r="L34" t="n">
         <v>1368.413344788622</v>
@@ -6879,22 +6879,22 @@
         <v>27.52</v>
       </c>
       <c r="T34" t="n">
-        <v>226.0067463719196</v>
+        <v>27.52</v>
       </c>
       <c r="U34" t="n">
-        <v>226.0067463719196</v>
+        <v>283.9777169005817</v>
       </c>
       <c r="V34" t="n">
-        <v>434.7281392578656</v>
+        <v>492.6991097865276</v>
       </c>
       <c r="W34" t="n">
-        <v>616.5190575175429</v>
+        <v>674.490028046205</v>
       </c>
       <c r="X34" t="n">
-        <v>777.4498485417364</v>
+        <v>835.4208190703985</v>
       </c>
       <c r="Y34" t="n">
-        <v>777.4498485417364</v>
+        <v>956.7301197494307</v>
       </c>
     </row>
     <row r="35">
@@ -6934,19 +6934,19 @@
         <v>360.59</v>
       </c>
       <c r="L35" t="n">
-        <v>642.6791164251993</v>
+        <v>402.6698853266331</v>
       </c>
       <c r="M35" t="n">
+        <v>736.2998853266331</v>
+      </c>
+      <c r="N35" t="n">
         <v>976.3091164251992</v>
       </c>
-      <c r="N35" t="n">
-        <v>1309.939116425199</v>
-      </c>
       <c r="O35" t="n">
-        <v>1309.939116425199</v>
+        <v>976.3091164251992</v>
       </c>
       <c r="P35" t="n">
-        <v>1348</v>
+        <v>1014.37</v>
       </c>
       <c r="Q35" t="n">
         <v>1348</v>
@@ -6955,22 +6955,22 @@
         <v>1348</v>
       </c>
       <c r="S35" t="n">
-        <v>1273.418507779456</v>
+        <v>1271.524819081964</v>
       </c>
       <c r="T35" t="n">
-        <v>1099.179602322961</v>
+        <v>1097.285913625468</v>
       </c>
       <c r="U35" t="n">
-        <v>860.5939974644587</v>
+        <v>858.7003087669661</v>
       </c>
       <c r="V35" t="n">
-        <v>641.5525589121113</v>
+        <v>639.6588702146188</v>
       </c>
       <c r="W35" t="n">
-        <v>413.9025831737804</v>
+        <v>412.0088944762879</v>
       </c>
       <c r="X35" t="n">
-        <v>232.8098221023988</v>
+        <v>230.9161334049063</v>
       </c>
       <c r="Y35" t="n">
         <v>133.499284038958</v>
@@ -6983,25 +6983,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26.96</v>
+        <v>771.9221712617338</v>
       </c>
       <c r="C36" t="n">
-        <v>26.96</v>
+        <v>771.9221712617338</v>
       </c>
       <c r="D36" t="n">
-        <v>26.96</v>
+        <v>771.9221712617338</v>
       </c>
       <c r="E36" t="n">
-        <v>26.96</v>
+        <v>431.5181308576933</v>
       </c>
       <c r="F36" t="n">
-        <v>26.96</v>
+        <v>91.11409045365292</v>
       </c>
       <c r="G36" t="n">
-        <v>26.96</v>
+        <v>91.11409045365292</v>
       </c>
       <c r="H36" t="n">
-        <v>26.96</v>
+        <v>91.11409045365292</v>
       </c>
       <c r="I36" t="n">
         <v>26.96</v>
@@ -7031,28 +7031,28 @@
         <v>1191.754201452346</v>
       </c>
       <c r="R36" t="n">
-        <v>1065.162143962426</v>
+        <v>851.3501610483054</v>
       </c>
       <c r="S36" t="n">
-        <v>1013.76097189983</v>
+        <v>799.9489889857097</v>
       </c>
       <c r="T36" t="n">
-        <v>734.2689720759759</v>
+        <v>799.9489889857097</v>
       </c>
       <c r="U36" t="n">
-        <v>393.8649316719354</v>
+        <v>799.9489889857097</v>
       </c>
       <c r="V36" t="n">
-        <v>53.46089126789501</v>
+        <v>798.4230625296287</v>
       </c>
       <c r="W36" t="n">
-        <v>33.89206004584601</v>
+        <v>778.8542313075798</v>
       </c>
       <c r="X36" t="n">
-        <v>26.96</v>
+        <v>771.9221712617338</v>
       </c>
       <c r="Y36" t="n">
-        <v>26.96</v>
+        <v>771.9221712617338</v>
       </c>
     </row>
     <row r="37">
@@ -7062,34 +7062,34 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>629.2832125532424</v>
+        <v>485.2831713199955</v>
       </c>
       <c r="C37" t="n">
-        <v>768.1552183716782</v>
+        <v>485.2831713199955</v>
       </c>
       <c r="D37" t="n">
-        <v>894.3443624966783</v>
+        <v>485.2831713199955</v>
       </c>
       <c r="E37" t="n">
-        <v>1025.043266708091</v>
+        <v>615.9820755314086</v>
       </c>
       <c r="F37" t="n">
-        <v>1162.274239300027</v>
+        <v>753.213048123344</v>
       </c>
       <c r="G37" t="n">
-        <v>1328.670416662322</v>
+        <v>919.6092254856392</v>
       </c>
       <c r="H37" t="n">
-        <v>1348</v>
+        <v>1103.059265399135</v>
       </c>
       <c r="I37" t="n">
-        <v>1348</v>
+        <v>1340.659187613906</v>
       </c>
       <c r="J37" t="n">
-        <v>1348</v>
+        <v>1340.659187613906</v>
       </c>
       <c r="K37" t="n">
-        <v>1348</v>
+        <v>1340.659187613906</v>
       </c>
       <c r="L37" t="n">
         <v>1348</v>
@@ -7107,31 +7107,31 @@
         <v>642.3510012754898</v>
       </c>
       <c r="Q37" t="n">
-        <v>336.5709341789262</v>
+        <v>338.2424607857296</v>
       </c>
       <c r="R37" t="n">
         <v>26.96</v>
       </c>
       <c r="S37" t="n">
-        <v>79.16475689745181</v>
+        <v>26.96</v>
       </c>
       <c r="T37" t="n">
-        <v>280.6215032693714</v>
+        <v>72.47574195047761</v>
       </c>
       <c r="U37" t="n">
-        <v>280.6215032693714</v>
+        <v>72.47574195047761</v>
       </c>
       <c r="V37" t="n">
-        <v>280.6215032693714</v>
+        <v>72.47574195047761</v>
       </c>
       <c r="W37" t="n">
-        <v>465.3824215290488</v>
+        <v>72.47574195047761</v>
       </c>
       <c r="X37" t="n">
-        <v>629.2832125532424</v>
+        <v>236.3765329746711</v>
       </c>
       <c r="Y37" t="n">
-        <v>629.2832125532424</v>
+        <v>360.6558336537034</v>
       </c>
     </row>
     <row r="38">
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>63.80300832625648</v>
+        <v>61.90931962876398</v>
       </c>
       <c r="C38" t="n">
         <v>26.96</v>
@@ -7165,25 +7165,25 @@
         <v>26.96</v>
       </c>
       <c r="J38" t="n">
-        <v>26.96</v>
+        <v>360.59</v>
       </c>
       <c r="K38" t="n">
-        <v>60.87929542713567</v>
+        <v>394.5092954271356</v>
       </c>
       <c r="L38" t="n">
-        <v>102.9591807537688</v>
+        <v>436.5891807537688</v>
       </c>
       <c r="M38" t="n">
-        <v>347.11</v>
+        <v>770.2191807537688</v>
       </c>
       <c r="N38" t="n">
-        <v>680.74</v>
+        <v>1103.849180753769</v>
       </c>
       <c r="O38" t="n">
-        <v>1014.37</v>
+        <v>1103.849180753769</v>
       </c>
       <c r="P38" t="n">
-        <v>1348</v>
+        <v>1141.91006432857</v>
       </c>
       <c r="Q38" t="n">
         <v>1348</v>
@@ -7192,25 +7192,25 @@
         <v>1348</v>
       </c>
       <c r="S38" t="n">
-        <v>1273.418507779456</v>
+        <v>1271.524819081964</v>
       </c>
       <c r="T38" t="n">
-        <v>1099.179602322961</v>
+        <v>1097.285913625468</v>
       </c>
       <c r="U38" t="n">
-        <v>860.5939974644587</v>
+        <v>858.7003087669661</v>
       </c>
       <c r="V38" t="n">
-        <v>641.5525589121113</v>
+        <v>639.6588702146188</v>
       </c>
       <c r="W38" t="n">
-        <v>413.9025831737804</v>
+        <v>412.0088944762879</v>
       </c>
       <c r="X38" t="n">
-        <v>232.8098221023988</v>
+        <v>230.9161334049063</v>
       </c>
       <c r="Y38" t="n">
-        <v>133.499284038958</v>
+        <v>131.6055953414655</v>
       </c>
     </row>
     <row r="39">
@@ -7220,22 +7220,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>361.0774313108504</v>
+        <v>985.7341541758541</v>
       </c>
       <c r="C39" t="n">
-        <v>361.0774313108504</v>
+        <v>985.7341541758541</v>
       </c>
       <c r="D39" t="n">
-        <v>361.0774313108504</v>
+        <v>985.7341541758541</v>
       </c>
       <c r="E39" t="n">
-        <v>361.0774313108504</v>
+        <v>645.3301137718137</v>
       </c>
       <c r="F39" t="n">
-        <v>361.0774313108504</v>
+        <v>304.9260733677733</v>
       </c>
       <c r="G39" t="n">
-        <v>361.0774313108504</v>
+        <v>304.9260733677733</v>
       </c>
       <c r="H39" t="n">
         <v>26.96</v>
@@ -7250,13 +7250,13 @@
         <v>376.6271300432672</v>
       </c>
       <c r="L39" t="n">
-        <v>642.6214735340828</v>
+        <v>678.9555789026183</v>
       </c>
       <c r="M39" t="n">
-        <v>764.851865276942</v>
+        <v>801.1859706454775</v>
       </c>
       <c r="N39" t="n">
-        <v>935.2387788467745</v>
+        <v>971.57288421531</v>
       </c>
       <c r="O39" t="n">
         <v>1208.226546662569</v>
@@ -7277,19 +7277,19 @@
         <v>1013.76097189983</v>
       </c>
       <c r="U39" t="n">
-        <v>727.9823629827858</v>
+        <v>1013.76097189983</v>
       </c>
       <c r="V39" t="n">
-        <v>387.5783225787454</v>
+        <v>1012.235045443749</v>
       </c>
       <c r="W39" t="n">
-        <v>368.0094913566964</v>
+        <v>992.6662142217001</v>
       </c>
       <c r="X39" t="n">
-        <v>361.0774313108504</v>
+        <v>985.7341541758541</v>
       </c>
       <c r="Y39" t="n">
-        <v>361.0774313108504</v>
+        <v>985.7341541758541</v>
       </c>
     </row>
     <row r="40">
@@ -7299,31 +7299,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>883.671095788587</v>
+        <v>593.0927932954676</v>
       </c>
       <c r="C40" t="n">
-        <v>883.671095788587</v>
+        <v>593.0927932954676</v>
       </c>
       <c r="D40" t="n">
-        <v>883.671095788587</v>
+        <v>593.0927932954676</v>
       </c>
       <c r="E40" t="n">
-        <v>1014.37</v>
+        <v>723.7916975068806</v>
       </c>
       <c r="F40" t="n">
-        <v>1014.37</v>
+        <v>861.0226700988161</v>
       </c>
       <c r="G40" t="n">
-        <v>1014.37</v>
+        <v>1027.418847461111</v>
       </c>
       <c r="H40" t="n">
-        <v>1014.37</v>
+        <v>1210.868887374607</v>
       </c>
       <c r="I40" t="n">
-        <v>1014.37</v>
+        <v>1210.868887374607</v>
       </c>
       <c r="J40" t="n">
-        <v>1348</v>
+        <v>1210.868887374607</v>
       </c>
       <c r="K40" t="n">
         <v>1348</v>
@@ -7332,16 +7332,16 @@
         <v>1348</v>
       </c>
       <c r="M40" t="n">
-        <v>1258.411536751854</v>
+        <v>1260.083063358657</v>
       </c>
       <c r="N40" t="n">
-        <v>1117.304091950185</v>
+        <v>1118.975618556988</v>
       </c>
       <c r="O40" t="n">
-        <v>904.810907502099</v>
+        <v>906.4824341089025</v>
       </c>
       <c r="P40" t="n">
-        <v>642.3510012754898</v>
+        <v>644.0225278822934</v>
       </c>
       <c r="Q40" t="n">
         <v>338.2424607857296</v>
@@ -7350,25 +7350,25 @@
         <v>26.96</v>
       </c>
       <c r="S40" t="n">
-        <v>74.41135527344574</v>
+        <v>79.16475689745182</v>
       </c>
       <c r="T40" t="n">
-        <v>74.41135527344574</v>
+        <v>280.6215032693714</v>
       </c>
       <c r="U40" t="n">
-        <v>74.41135527344574</v>
+        <v>540.0492201699531</v>
       </c>
       <c r="V40" t="n">
-        <v>286.1027481593917</v>
+        <v>593.0927932954676</v>
       </c>
       <c r="W40" t="n">
-        <v>470.8636664190691</v>
+        <v>593.0927932954676</v>
       </c>
       <c r="X40" t="n">
-        <v>634.7644574432626</v>
+        <v>593.0927932954676</v>
       </c>
       <c r="Y40" t="n">
-        <v>759.0437581222949</v>
+        <v>593.0927932954676</v>
       </c>
     </row>
     <row r="41">
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26.96</v>
+        <v>359.6926778205164</v>
       </c>
       <c r="C41" t="n">
-        <v>26.96</v>
+        <v>359.6926778205164</v>
       </c>
       <c r="D41" t="n">
-        <v>26.96</v>
+        <v>359.6926778205164</v>
       </c>
       <c r="E41" t="n">
-        <v>26.96</v>
+        <v>304.3628946754609</v>
       </c>
       <c r="F41" t="n">
-        <v>26.96</v>
+        <v>211.5450878996913</v>
       </c>
       <c r="G41" t="n">
-        <v>26.96</v>
+        <v>120.1430418862086</v>
       </c>
       <c r="H41" t="n">
         <v>26.96</v>
@@ -7411,16 +7411,16 @@
         <v>436.5891807537688</v>
       </c>
       <c r="M41" t="n">
-        <v>436.5891807537689</v>
+        <v>770.2191807537688</v>
       </c>
       <c r="N41" t="n">
-        <v>680.74</v>
+        <v>1103.849180753769</v>
       </c>
       <c r="O41" t="n">
-        <v>680.74</v>
+        <v>1103.849180753769</v>
       </c>
       <c r="P41" t="n">
-        <v>1014.37</v>
+        <v>1141.91006432857</v>
       </c>
       <c r="Q41" t="n">
         <v>1348</v>
@@ -7429,25 +7429,25 @@
         <v>1348</v>
       </c>
       <c r="S41" t="n">
-        <v>1290.51632864608</v>
+        <v>1348</v>
       </c>
       <c r="T41" t="n">
-        <v>1015.267322179483</v>
+        <v>1348</v>
       </c>
       <c r="U41" t="n">
-        <v>675.6716163108803</v>
+        <v>1008.404294131397</v>
       </c>
       <c r="V41" t="n">
-        <v>355.6200767484319</v>
+        <v>688.3527545689483</v>
       </c>
       <c r="W41" t="n">
-        <v>26.96</v>
+        <v>359.6926778205164</v>
       </c>
       <c r="X41" t="n">
-        <v>26.96</v>
+        <v>359.6926778205164</v>
       </c>
       <c r="Y41" t="n">
-        <v>26.96</v>
+        <v>359.6926778205164</v>
       </c>
     </row>
     <row r="42">
@@ -7469,10 +7469,10 @@
         <v>182.752263365195</v>
       </c>
       <c r="F42" t="n">
-        <v>155.8469680744103</v>
+        <v>57.63846430830512</v>
       </c>
       <c r="G42" t="n">
-        <v>143.1243189153394</v>
+        <v>44.91581514923423</v>
       </c>
       <c r="H42" t="n">
         <v>26.96</v>
@@ -7481,22 +7481,22 @@
         <v>26.96</v>
       </c>
       <c r="J42" t="n">
-        <v>164.3959025337895</v>
+        <v>128.0617971652541</v>
       </c>
       <c r="K42" t="n">
-        <v>376.6271300432672</v>
+        <v>340.2930246747318</v>
       </c>
       <c r="L42" t="n">
-        <v>678.9555789026183</v>
+        <v>642.6214735340828</v>
       </c>
       <c r="M42" t="n">
-        <v>801.1859706454775</v>
+        <v>764.851865276942</v>
       </c>
       <c r="N42" t="n">
-        <v>971.57288421531</v>
+        <v>935.2387788467745</v>
       </c>
       <c r="O42" t="n">
-        <v>1244.560652031104</v>
+        <v>1208.226546662569</v>
       </c>
       <c r="P42" t="n">
         <v>1348</v>
@@ -7554,7 +7554,7 @@
         <v>808.4914078967222</v>
       </c>
       <c r="H43" t="n">
-        <v>887.8586931959089</v>
+        <v>892.9414478102182</v>
       </c>
       <c r="I43" t="n">
         <v>1026.45861541068</v>
@@ -7566,22 +7566,22 @@
         <v>1348</v>
       </c>
       <c r="L43" t="n">
-        <v>1348</v>
+        <v>1254.479759602177</v>
       </c>
       <c r="M43" t="n">
-        <v>1348</v>
+        <v>1063.88119534393</v>
       </c>
       <c r="N43" t="n">
-        <v>1348</v>
+        <v>821.7636495321601</v>
       </c>
       <c r="O43" t="n">
-        <v>1095.917497298794</v>
+        <v>508.2603640739731</v>
       </c>
       <c r="P43" t="n">
-        <v>755.5134568947537</v>
+        <v>508.2603640739731</v>
       </c>
       <c r="Q43" t="n">
-        <v>415.1094164907134</v>
+        <v>167.8563236699327</v>
       </c>
       <c r="R43" t="n">
         <v>74.70537608667298</v>
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>570.8414138500505</v>
+        <v>125.8384128363756</v>
       </c>
       <c r="C44" t="n">
-        <v>426.9276984530869</v>
+        <v>125.8384128363756</v>
       </c>
       <c r="D44" t="n">
-        <v>322.544712857279</v>
+        <v>125.8384128363756</v>
       </c>
       <c r="E44" t="n">
-        <v>322.544712857279</v>
+        <v>125.8384128363756</v>
       </c>
       <c r="F44" t="n">
-        <v>223.6663000209034</v>
+        <v>26.96</v>
       </c>
       <c r="G44" t="n">
-        <v>126.2036479468147</v>
+        <v>26.96</v>
       </c>
       <c r="H44" t="n">
         <v>26.96</v>
@@ -7642,7 +7642,7 @@
         <v>26.96</v>
       </c>
       <c r="K44" t="n">
-        <v>266.9692310985661</v>
+        <v>60.87929542713567</v>
       </c>
       <c r="L44" t="n">
         <v>309.0491164251993</v>
@@ -7672,19 +7672,19 @@
         <v>1164.454112011257</v>
       </c>
       <c r="U44" t="n">
-        <v>1164.454112011257</v>
+        <v>824.0500716072165</v>
       </c>
       <c r="V44" t="n">
-        <v>1164.454112011257</v>
+        <v>824.0500716072165</v>
       </c>
       <c r="W44" t="n">
-        <v>1164.454112011257</v>
+        <v>797.1501088960207</v>
       </c>
       <c r="X44" t="n">
-        <v>876.2906438691683</v>
+        <v>508.9866407539321</v>
       </c>
       <c r="Y44" t="n">
-        <v>747.6083966334591</v>
+        <v>302.6053956197842</v>
       </c>
     </row>
     <row r="45">
@@ -7718,22 +7718,22 @@
         <v>26.96</v>
       </c>
       <c r="J45" t="n">
-        <v>164.3959025337895</v>
+        <v>128.0617971652541</v>
       </c>
       <c r="K45" t="n">
-        <v>376.6271300432672</v>
+        <v>340.2930246747318</v>
       </c>
       <c r="L45" t="n">
-        <v>678.9555789026183</v>
+        <v>642.6214735340828</v>
       </c>
       <c r="M45" t="n">
-        <v>801.1859706454775</v>
+        <v>764.851865276942</v>
       </c>
       <c r="N45" t="n">
-        <v>971.57288421531</v>
+        <v>935.2387788467745</v>
       </c>
       <c r="O45" t="n">
-        <v>1244.560652031104</v>
+        <v>1208.226546662569</v>
       </c>
       <c r="P45" t="n">
         <v>1348</v>
@@ -7812,16 +7812,16 @@
         <v>961.8027378370269</v>
       </c>
       <c r="O46" t="n">
-        <v>961.8027378370269</v>
+        <v>642.2388463182339</v>
       </c>
       <c r="P46" t="n">
-        <v>707.7680808080809</v>
+        <v>301.8348059141935</v>
       </c>
       <c r="Q46" t="n">
-        <v>367.3640404040404</v>
+        <v>301.8348059141935</v>
       </c>
       <c r="R46" t="n">
-        <v>26.96</v>
+        <v>80.76598214727905</v>
       </c>
       <c r="S46" t="n">
         <v>26.96</v>
@@ -7964,16 +7964,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>12.18253890840691</v>
+        <v>358.1825389084069</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>216.8080158297278</v>
       </c>
       <c r="M2" t="n">
-        <v>842.9671979940761</v>
+        <v>496.9671979940761</v>
       </c>
       <c r="N2" t="n">
         <v>775.1887470145589</v>
@@ -7982,10 +7982,10 @@
         <v>24.86597510173064</v>
       </c>
       <c r="P2" t="n">
-        <v>307.5546630557568</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>398.989620016029</v>
+        <v>489.7362672420583</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8049,7 +8049,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L3" t="n">
-        <v>387.0245835623135</v>
+        <v>387.0245835622875</v>
       </c>
       <c r="M3" t="n">
         <v>471.6948204301074</v>
@@ -8201,7 +8201,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>12.18253890840691</v>
+        <v>228.9905547381346</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -8216,13 +8216,13 @@
         <v>775.1887470145589</v>
       </c>
       <c r="O5" t="n">
-        <v>370.8659751017306</v>
+        <v>24.86597510173064</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>360.5442830717859</v>
+        <v>489.7362672420583</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,7 +8438,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>364.1825389084069</v>
+        <v>364.1825389084129</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -8447,10 +8447,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>848.9671979940761</v>
+        <v>848.9671979940821</v>
       </c>
       <c r="N8" t="n">
-        <v>781.1887470145589</v>
+        <v>781.1887470145649</v>
       </c>
       <c r="O8" t="n">
         <v>24.86597510173064</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>366.3018588293617</v>
+        <v>366.3018588293435</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,7 +8675,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>12.18253890840691</v>
+        <v>371.1825389084206</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -8684,19 +8684,19 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>726.2499612985511</v>
+        <v>855.9671979940898</v>
       </c>
       <c r="N11" t="n">
-        <v>788.1887470145589</v>
+        <v>788.1887470145725</v>
       </c>
       <c r="O11" t="n">
-        <v>383.8659751017306</v>
+        <v>24.86597510173064</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>502.7362672420583</v>
+        <v>373.0190305464923</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,19 +8912,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>12.18253890840691</v>
+        <v>371.1825389084161</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>316.4950653266332</v>
+        <v>229.2827633044478</v>
       </c>
       <c r="M14" t="n">
-        <v>855.9671979940761</v>
+        <v>855.9671979940853</v>
       </c>
       <c r="N14" t="n">
-        <v>788.1887470145589</v>
+        <v>788.188747014568</v>
       </c>
       <c r="O14" t="n">
         <v>24.86597510173064</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>415.5239652199002</v>
+        <v>143.7362672420583</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9152,16 +9152,16 @@
         <v>12.18253890840691</v>
       </c>
       <c r="K17" t="n">
-        <v>324.7380854271357</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>229.2827633044473</v>
       </c>
       <c r="M17" t="n">
-        <v>855.9671979940761</v>
+        <v>855.9671979940853</v>
       </c>
       <c r="N17" t="n">
-        <v>692.7334248918982</v>
+        <v>788.1887470145682</v>
       </c>
       <c r="O17" t="n">
         <v>24.86597510173064</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>502.7362672420583</v>
+        <v>502.7362672420676</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,28 +9386,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>12.18253890840691</v>
+        <v>371.1825389084162</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>324.7380854271356</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>855.9671979940761</v>
+        <v>760.511875871397</v>
       </c>
       <c r="N20" t="n">
-        <v>788.1887470145589</v>
+        <v>429.1887470145588</v>
       </c>
       <c r="O20" t="n">
-        <v>383.8659751017306</v>
+        <v>24.86597510173064</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>373.0190305465333</v>
+        <v>502.7362672420676</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9626,16 +9626,16 @@
         <v>12.18253890840691</v>
       </c>
       <c r="K23" t="n">
-        <v>324.7380854271357</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>263.5446778773393</v>
+        <v>316.4950653266332</v>
       </c>
       <c r="M23" t="n">
-        <v>855.9671979940761</v>
+        <v>855.9671979940865</v>
       </c>
       <c r="N23" t="n">
-        <v>788.1887470145589</v>
+        <v>700.97644499238</v>
       </c>
       <c r="O23" t="n">
         <v>24.86597510173064</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>143.7362672420583</v>
+        <v>502.7362672420687</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,28 +9860,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>12.18253890840691</v>
+        <v>362.1825389084303</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>259.0917366122845</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>846.9671979940761</v>
+        <v>496.9671979940761</v>
       </c>
       <c r="N26" t="n">
-        <v>649.8351466826704</v>
+        <v>429.1887470145588</v>
       </c>
       <c r="O26" t="n">
-        <v>374.8659751017306</v>
+        <v>24.86597510173064</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>311.5546630557802</v>
       </c>
       <c r="Q26" t="n">
-        <v>493.7362672420583</v>
+        <v>493.7362672420817</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,25 +10100,25 @@
         <v>12.18253890840691</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>220.6463996680591</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>846.9671979940761</v>
+        <v>846.9671979940935</v>
       </c>
       <c r="N29" t="n">
-        <v>688.2804836269136</v>
+        <v>779.1887470145764</v>
       </c>
       <c r="O29" t="n">
-        <v>374.8659751017306</v>
+        <v>24.86597510173064</v>
       </c>
       <c r="P29" t="n">
-        <v>311.5546630557568</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>143.7362672420583</v>
+        <v>493.7362672420758</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,22 +10334,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>356.1825389084069</v>
+        <v>12.18253890840691</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>214.8888239105358</v>
       </c>
       <c r="M32" t="n">
-        <v>496.9671979940761</v>
+        <v>840.9671979940761</v>
       </c>
       <c r="N32" t="n">
-        <v>644.0775709250947</v>
+        <v>773.1887470145589</v>
       </c>
       <c r="O32" t="n">
-        <v>368.8659751017306</v>
+        <v>24.86597510173064</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -10419,7 +10419,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L33" t="n">
-        <v>379.1053916430956</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M33" t="n">
         <v>471.6948204301074</v>
@@ -10428,7 +10428,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O33" t="n">
-        <v>382.6817988009037</v>
+        <v>373.6978539842012</v>
       </c>
       <c r="P33" t="n">
         <v>219.1507118405495</v>
@@ -10577,13 +10577,13 @@
         <v>302.7380854271357</v>
       </c>
       <c r="L35" t="n">
-        <v>242.4335667662284</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>833.9671979940761</v>
       </c>
       <c r="N35" t="n">
-        <v>766.1887470145589</v>
+        <v>671.6223137807873</v>
       </c>
       <c r="O35" t="n">
         <v>24.86597510173064</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>143.7362672420583</v>
+        <v>480.7362672420583</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10808,7 +10808,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>12.18253890840691</v>
+        <v>349.1825389084069</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -10817,19 +10817,19 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>743.5841871316834</v>
+        <v>833.9671979940761</v>
       </c>
       <c r="N38" t="n">
         <v>766.1887470145589</v>
       </c>
       <c r="O38" t="n">
-        <v>361.8659751017306</v>
+        <v>24.86597510173064</v>
       </c>
       <c r="P38" t="n">
-        <v>298.5546630557568</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>143.7362672420583</v>
+        <v>351.9079194354223</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -10893,7 +10893,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L39" t="n">
-        <v>351.3882199259239</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M39" t="n">
         <v>471.6948204301074</v>
@@ -10902,7 +10902,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O39" t="n">
-        <v>382.6817988009037</v>
+        <v>345.9806822670295</v>
       </c>
       <c r="P39" t="n">
         <v>219.1507118405495</v>
@@ -11054,19 +11054,19 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>496.9671979940761</v>
+        <v>833.9671979940761</v>
       </c>
       <c r="N41" t="n">
-        <v>675.8057361521661</v>
+        <v>766.1887470145589</v>
       </c>
       <c r="O41" t="n">
         <v>24.86597510173064</v>
       </c>
       <c r="P41" t="n">
-        <v>298.5546630557568</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>480.7362672420583</v>
+        <v>351.9079194354223</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11124,7 +11124,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J42" t="n">
-        <v>227.4647419277884</v>
+        <v>190.7636253939142</v>
       </c>
       <c r="K42" t="n">
         <v>295.8802408630135</v>
@@ -11142,7 +11142,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P42" t="n">
-        <v>182.4495953066751</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q42" t="n">
         <v>17.27519534353338</v>
@@ -11285,10 +11285,10 @@
         <v>12.18253890840691</v>
       </c>
       <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
         <v>208.1716521933641</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>833.9671979940761</v>
@@ -11361,7 +11361,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J45" t="n">
-        <v>227.4647419277884</v>
+        <v>190.7636253939142</v>
       </c>
       <c r="K45" t="n">
         <v>295.8802408630135</v>
@@ -11379,7 +11379,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P45" t="n">
-        <v>182.4495953066751</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q45" t="n">
         <v>17.27519534353338</v>
@@ -22518,7 +22518,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3.339155739849787</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -22563,7 +22563,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>20.94755181051743</v>
+        <v>24.28670755036733</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -22749,7 +22749,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>24.28670755036728</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -22806,7 +22806,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>24.28670755036725</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1.001907550367306</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -23037,7 +23037,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.001907550367338</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -23274,7 +23274,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>61.82846288594217</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -23286,7 +23286,7 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>61.82846288594229</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -23463,7 +23463,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>49.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -23472,13 +23472,13 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>4.889628708011855</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>5.251211467346479</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23514,10 +23514,10 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>61.82846288594226</v>
       </c>
       <c r="U14" t="n">
-        <v>2.213044467590009</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -23709,13 +23709,13 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8896287080118555</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7494253121827501</v>
+        <v>0.7494253121785154</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23751,10 +23751,10 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>4.199597157236099</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>5.089225865248039</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>5.838651177423202</v>
+        <v>5.838651177423898</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -24189,7 +24189,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.7494253121827501</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -24222,7 +24222,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>5.838651177424566</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -24234,7 +24234,7 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>5.089225865247926</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -24408,7 +24408,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>125.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -24426,7 +24426,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>49.25121146734648</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24465,16 +24465,16 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>293.1997488099172</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>273.8510241668239</v>
       </c>
       <c r="W26" t="n">
-        <v>168.5128758934979</v>
+        <v>12.99446080034551</v>
       </c>
       <c r="X26" t="n">
-        <v>236.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -24602,19 +24602,19 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>196.6963703536521</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>75.88406070941889</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>272.580431063118</v>
       </c>
       <c r="Q28" t="n">
-        <v>9.722266425597979</v>
+        <v>9.72226642557456</v>
       </c>
       <c r="R28" t="n">
-        <v>15.16963617787235</v>
+        <v>15.16963617784893</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -24648,19 +24648,19 @@
         <v>119.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>87.47457824299391</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>48.33915573984979</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>42.36328960686865</v>
       </c>
       <c r="F29" t="n">
-        <v>42.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>41.48802555334787</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -24699,7 +24699,7 @@
         <v>126.7104291088556</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>162.3808716784517</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -24711,10 +24711,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>189.8388594306939</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>149.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -24836,10 +24836,10 @@
         <v>43.58503799384475</v>
       </c>
       <c r="M31" t="n">
-        <v>139.6925786156646</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>104.6199301216002</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -24848,10 +24848,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.722266425597999</v>
+        <v>248.0347751628805</v>
       </c>
       <c r="R31" t="n">
-        <v>9.16963617787237</v>
+        <v>9.169636177854862</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -24882,7 +24882,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>2.048307550367326</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -24939,7 +24939,7 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>2.048307550367298</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -25170,7 +25170,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.874751810517384</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -25188,7 +25188,7 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.874751810517566</v>
       </c>
     </row>
     <row r="36">
@@ -25322,10 +25322,10 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1.654811340735421</v>
       </c>
       <c r="R37" t="n">
-        <v>1.654811340735421</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -25359,7 +25359,7 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>1.874751810517573</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -25407,7 +25407,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.874751810517384</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -25547,7 +25547,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1.65481134073525</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -25559,7 +25559,7 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.654811340735421</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -25602,16 +25602,16 @@
         <v>97.33915573984979</v>
       </c>
       <c r="E41" t="n">
-        <v>91.36328960686865</v>
+        <v>36.5868042932637</v>
       </c>
       <c r="F41" t="n">
-        <v>91.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>90.48802555334787</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>92.25121146734651</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25644,10 +25644,10 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>118.8015944684749</v>
+        <v>175.7104291088556</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>272.4965164019307</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -25781,25 +25781,25 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>92.58503799384475</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>188.6925786156646</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>239.6963703536521</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>60.80657492941133</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>22.83530716434304</v>
+        <v>359.835307164343</v>
       </c>
       <c r="Q43" t="n">
         <v>65.72226642559799</v>
       </c>
       <c r="R43" t="n">
-        <v>71.16963617787238</v>
+        <v>315.9501980704453</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -25833,10 +25833,10 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>142.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>103.3391557398498</v>
       </c>
       <c r="E44" t="n">
         <v>97.36328960686865</v>
@@ -25845,10 +25845,10 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>96.48802555334787</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>98.25121146734651</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25887,19 +25887,19 @@
         <v>278.4965164019307</v>
       </c>
       <c r="U44" t="n">
-        <v>342.1997488099172</v>
+        <v>5.1997488099172</v>
       </c>
       <c r="V44" t="n">
         <v>322.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>331.3734759809475</v>
+        <v>304.7425128968637</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>76.9220079194542</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -26027,19 +26027,19 @@
         <v>245.6963703536521</v>
       </c>
       <c r="O46" t="n">
-        <v>316.3682526036051</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>114.3409967056864</v>
+        <v>28.83530716434304</v>
       </c>
       <c r="Q46" t="n">
-        <v>71.72226642559799</v>
+        <v>408.722266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>77.16963617787238</v>
+        <v>195.3115006486271</v>
       </c>
       <c r="S46" t="n">
-        <v>53.26792232580625</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>871935.3373781984</v>
+        <v>871935.3373781979</v>
       </c>
     </row>
     <row r="3">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4487386.355767606</v>
+        <v>4487386.355767607</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5211260.918894454</v>
+        <v>5211260.918894455</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5935135.482021303</v>
+        <v>5935135.482021304</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6620588.567247884</v>
+        <v>6620588.567247887</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7311801.324348017</v>
+        <v>7311801.32434802</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8034826.961471941</v>
+        <v>8034826.961471945</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8757338.443149047</v>
+        <v>8757338.443149051</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9481371.597553425</v>
+        <v>9481371.597553428</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10132795.10699747</v>
+        <v>10132795.10699748</v>
       </c>
     </row>
     <row r="16">
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1477419.567993806</v>
+        <v>1477419.567993805</v>
       </c>
       <c r="C2" t="n">
         <v>1477419.567993805</v>
@@ -26278,28 +26278,28 @@
         <v>1479674.313977614</v>
       </c>
       <c r="E2" t="n">
+        <v>1473985.206257077</v>
+      </c>
+      <c r="F2" t="n">
         <v>1473985.206257078</v>
       </c>
-      <c r="F2" t="n">
-        <v>1473985.206257077</v>
-      </c>
       <c r="G2" t="n">
-        <v>1479221.933346175</v>
+        <v>1479221.933346176</v>
       </c>
       <c r="H2" t="n">
         <v>1479221.933346176</v>
       </c>
       <c r="I2" t="n">
-        <v>1479221.933346176</v>
+        <v>1479221.933346174</v>
       </c>
       <c r="J2" t="n">
-        <v>1403316.967360253</v>
+        <v>1403316.967360254</v>
       </c>
       <c r="K2" t="n">
-        <v>1412478.242769842</v>
+        <v>1412478.242769843</v>
       </c>
       <c r="L2" t="n">
-        <v>1479576.444185613</v>
+        <v>1479576.444185614</v>
       </c>
       <c r="M2" t="n">
         <v>1479546.011174153</v>
@@ -26308,7 +26308,7 @@
         <v>1479546.011174153</v>
       </c>
       <c r="O2" t="n">
-        <v>1331169.780168255</v>
+        <v>1331169.780168254</v>
       </c>
       <c r="P2" t="n">
         <v>1319448.233791577</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>662429.5962486186</v>
+        <v>662414.3467159418</v>
       </c>
       <c r="C4" t="n">
-        <v>660385.8053318618</v>
+        <v>660370.5557991849</v>
       </c>
       <c r="D4" t="n">
-        <v>659247.423067487</v>
+        <v>659232.0843253952</v>
       </c>
       <c r="E4" t="n">
-        <v>654268.4461200006</v>
+        <v>654253.00572693</v>
       </c>
       <c r="F4" t="n">
-        <v>652232.3336778827</v>
+        <v>652216.8932848121</v>
       </c>
       <c r="G4" t="n">
-        <v>652687.3325291139</v>
+        <v>652671.8921360434</v>
       </c>
       <c r="H4" t="n">
-        <v>650635.2986551896</v>
+        <v>650619.8582621189</v>
       </c>
       <c r="I4" t="n">
-        <v>648580.4001086704</v>
+        <v>648564.9597155994</v>
       </c>
       <c r="J4" t="n">
-        <v>610931.7837333367</v>
+        <v>610916.4740343819</v>
       </c>
       <c r="K4" t="n">
-        <v>613319.658239872</v>
+        <v>613304.348540917</v>
       </c>
       <c r="L4" t="n">
-        <v>642943.0329629187</v>
+        <v>642927.8279435922</v>
       </c>
       <c r="M4" t="n">
-        <v>641094.9469295284</v>
+        <v>641079.8977069283</v>
       </c>
       <c r="N4" t="n">
-        <v>639005.4144827749</v>
+        <v>638990.3652601747</v>
       </c>
       <c r="O4" t="n">
-        <v>568368.0107265246</v>
+        <v>568352.9615039246</v>
       </c>
       <c r="P4" t="n">
-        <v>561149.5779135363</v>
+        <v>561134.5286909363</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>565559.4887451869</v>
+        <v>565574.7382778635</v>
       </c>
       <c r="C6" t="n">
-        <v>760320.2796619432</v>
+        <v>760335.5291946199</v>
       </c>
       <c r="D6" t="n">
-        <v>761236.6079101269</v>
+        <v>761251.9466522187</v>
       </c>
       <c r="E6" t="n">
-        <v>445937.3601370773</v>
+        <v>445952.8005301469</v>
       </c>
       <c r="F6" t="n">
-        <v>764837.4725791947</v>
+        <v>764852.9129722662</v>
       </c>
       <c r="G6" t="n">
-        <v>760482.9248170611</v>
+        <v>760498.3652101322</v>
       </c>
       <c r="H6" t="n">
-        <v>771334.9586909863</v>
+        <v>771350.399084057</v>
       </c>
       <c r="I6" t="n">
-        <v>773389.8572375057</v>
+        <v>773405.297630575</v>
       </c>
       <c r="J6" t="n">
-        <v>345092.0196269167</v>
+        <v>345107.3293258718</v>
       </c>
       <c r="K6" t="n">
-        <v>741185.0065299701</v>
+        <v>741200.3162289255</v>
       </c>
       <c r="L6" t="n">
-        <v>732589.3212226945</v>
+        <v>732604.5262420215</v>
       </c>
       <c r="M6" t="n">
-        <v>779380.3672446244</v>
+        <v>779395.4164672245</v>
       </c>
       <c r="N6" t="n">
-        <v>783869.8996913783</v>
+        <v>783884.9489139783</v>
       </c>
       <c r="O6" t="n">
-        <v>518537.97244173</v>
+        <v>518553.0216643296</v>
       </c>
       <c r="P6" t="n">
-        <v>710539.2728780406</v>
+        <v>710554.3221006406</v>
       </c>
     </row>
   </sheetData>
@@ -26990,10 +26990,10 @@
         <v>11</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>345</v>
@@ -27008,7 +27008,7 @@
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
         <v>245</v>
@@ -27518,7 +27518,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>60.45093135375322</v>
+        <v>290.4780005106055</v>
       </c>
       <c r="E3" t="n">
         <v>342.6720972219126</v>
@@ -27533,7 +27533,7 @@
         <v>330.7762569977419</v>
       </c>
       <c r="I3" t="n">
-        <v>212.1645934385184</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27572,10 +27572,10 @@
         <v>400.2008786281113</v>
       </c>
       <c r="V3" t="n">
+        <v>68.51066719152016</v>
+      </c>
+      <c r="W3" t="n">
         <v>407</v>
-      </c>
-      <c r="W3" t="n">
-        <v>86.37314290982852</v>
       </c>
       <c r="X3" t="n">
         <v>407</v>
@@ -27603,7 +27603,7 @@
         <v>407</v>
       </c>
       <c r="F4" t="n">
-        <v>407</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
         <v>244.9230531693989</v>
@@ -27612,16 +27612,16 @@
         <v>227.6969293803072</v>
       </c>
       <c r="I4" t="n">
-        <v>173.0000785709379</v>
+        <v>278.8779820233847</v>
       </c>
       <c r="J4" t="n">
         <v>26.72699801623563</v>
       </c>
       <c r="K4" t="n">
-        <v>407</v>
+        <v>274.4837246208152</v>
       </c>
       <c r="L4" t="n">
-        <v>407</v>
+        <v>405.5850379938448</v>
       </c>
       <c r="M4" t="n">
         <v>407</v>
@@ -27648,7 +27648,7 @@
         <v>209.508336998061</v>
       </c>
       <c r="U4" t="n">
-        <v>246.3295220348487</v>
+        <v>407</v>
       </c>
       <c r="V4" t="n">
         <v>199.1703102162162</v>
@@ -27749,16 +27749,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>384.5565566463266</v>
+        <v>38.55655664632661</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>15.09991244551929</v>
       </c>
       <c r="D6" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
@@ -27794,22 +27794,22 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>154.6833405621777</v>
       </c>
       <c r="R6" t="n">
-        <v>192.3261369150208</v>
+        <v>332.8751440256231</v>
       </c>
       <c r="S6" t="n">
-        <v>117.8871603419698</v>
+        <v>407</v>
       </c>
       <c r="T6" t="n">
         <v>404.7768878590232</v>
       </c>
       <c r="U6" t="n">
-        <v>54.20087862811128</v>
+        <v>400.2008786281113</v>
       </c>
       <c r="V6" t="n">
-        <v>302.6730901088973</v>
+        <v>407</v>
       </c>
       <c r="W6" t="n">
         <v>407</v>
@@ -27828,13 +27828,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>407</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
         <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>294.8769269415662</v>
       </c>
       <c r="E7" t="n">
         <v>407</v>
@@ -27843,16 +27843,16 @@
         <v>407</v>
       </c>
       <c r="G7" t="n">
-        <v>244.9230531693989</v>
+        <v>407</v>
       </c>
       <c r="H7" t="n">
-        <v>227.6969293803072</v>
+        <v>407</v>
       </c>
       <c r="I7" t="n">
-        <v>173.0000785709379</v>
+        <v>407</v>
       </c>
       <c r="J7" t="n">
-        <v>176.1918944434818</v>
+        <v>372.7269980162357</v>
       </c>
       <c r="K7" t="n">
         <v>407</v>
@@ -27882,13 +27882,13 @@
         <v>407</v>
       </c>
       <c r="T7" t="n">
-        <v>407</v>
+        <v>209.508336998061</v>
       </c>
       <c r="U7" t="n">
-        <v>407</v>
+        <v>150.9518011105235</v>
       </c>
       <c r="V7" t="n">
-        <v>407</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
         <v>226.3728098387097</v>
@@ -27986,16 +27986,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>32.55655664632056</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>9.099912445513283</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
@@ -28034,22 +28034,22 @@
         <v>154.6833405621777</v>
       </c>
       <c r="R9" t="n">
+        <v>343.8315797108015</v>
+      </c>
+      <c r="S9" t="n">
         <v>407</v>
       </c>
-      <c r="S9" t="n">
-        <v>327.7863395790482</v>
-      </c>
       <c r="T9" t="n">
-        <v>52.77688785902325</v>
+        <v>404.7768878590232</v>
       </c>
       <c r="U9" t="n">
-        <v>48.20087862811128</v>
+        <v>400.2008786281113</v>
       </c>
       <c r="V9" t="n">
         <v>407</v>
       </c>
       <c r="W9" t="n">
-        <v>80.37314290982852</v>
+        <v>407</v>
       </c>
       <c r="X9" t="n">
         <v>407</v>
@@ -28086,13 +28086,13 @@
         <v>407</v>
       </c>
       <c r="I10" t="n">
-        <v>173.0000785709379</v>
+        <v>407</v>
       </c>
       <c r="J10" t="n">
         <v>26.72699801623563</v>
       </c>
       <c r="K10" t="n">
-        <v>274.4837246208152</v>
+        <v>318.1113593559347</v>
       </c>
       <c r="L10" t="n">
         <v>405.5850379938448</v>
@@ -28116,7 +28116,7 @@
         <v>407</v>
       </c>
       <c r="S10" t="n">
-        <v>407</v>
+        <v>360.2679223258062</v>
       </c>
       <c r="T10" t="n">
         <v>209.508336998061</v>
@@ -28128,10 +28128,10 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>297.711933758805</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>407</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
         <v>407</v>
@@ -28223,16 +28223,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C12" t="n">
-        <v>361.0999124455193</v>
+        <v>2.099912445505609</v>
       </c>
       <c r="D12" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>339.6362423378769</v>
@@ -28271,10 +28271,10 @@
         <v>154.6833405621777</v>
       </c>
       <c r="R12" t="n">
-        <v>179.3261369150208</v>
+        <v>400</v>
       </c>
       <c r="S12" t="n">
-        <v>236.4379691511618</v>
+        <v>400</v>
       </c>
       <c r="T12" t="n">
         <v>400</v>
@@ -28286,13 +28286,13 @@
         <v>400</v>
       </c>
       <c r="W12" t="n">
-        <v>73.37314290982852</v>
+        <v>400</v>
       </c>
       <c r="X12" t="n">
-        <v>400</v>
+        <v>390.8093461979513</v>
       </c>
       <c r="Y12" t="n">
-        <v>399.3913927661343</v>
+        <v>40.39139276612067</v>
       </c>
     </row>
     <row r="13">
@@ -28308,16 +28308,16 @@
         <v>400</v>
       </c>
       <c r="D13" t="n">
-        <v>285.5362180555555</v>
+        <v>347.9098457426134</v>
       </c>
       <c r="E13" t="n">
         <v>280.9809048369565</v>
       </c>
       <c r="F13" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G13" t="n">
-        <v>400</v>
+        <v>244.9230531693989</v>
       </c>
       <c r="H13" t="n">
         <v>227.6969293803072</v>
@@ -28365,10 +28365,10 @@
         <v>400</v>
       </c>
       <c r="W13" t="n">
-        <v>334.235891394091</v>
+        <v>400</v>
       </c>
       <c r="X13" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y13" t="n">
         <v>400</v>
@@ -28460,13 +28460,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>384.5565566463266</v>
+        <v>25.55655664631743</v>
       </c>
       <c r="C15" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D15" t="n">
-        <v>347.9376868977026</v>
+        <v>302.8390535185254</v>
       </c>
       <c r="E15" t="n">
         <v>342.6720972219126</v>
@@ -28517,19 +28517,19 @@
         <v>400</v>
       </c>
       <c r="U15" t="n">
-        <v>41.20087862811128</v>
+        <v>400</v>
       </c>
       <c r="V15" t="n">
         <v>400</v>
       </c>
       <c r="W15" t="n">
-        <v>387.0736309025121</v>
+        <v>73.37314290981939</v>
       </c>
       <c r="X15" t="n">
-        <v>60.86273944538755</v>
+        <v>60.86273944537842</v>
       </c>
       <c r="Y15" t="n">
-        <v>40.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="16">
@@ -28539,19 +28539,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C16" t="n">
         <v>272.7252466480447</v>
       </c>
       <c r="D16" t="n">
-        <v>349.5674550623105</v>
+        <v>400</v>
       </c>
       <c r="E16" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F16" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G16" t="n">
         <v>244.9230531693989</v>
@@ -28566,7 +28566,7 @@
         <v>26.72699801623563</v>
       </c>
       <c r="K16" t="n">
-        <v>274.4837246208152</v>
+        <v>400</v>
       </c>
       <c r="L16" t="n">
         <v>400</v>
@@ -28590,7 +28590,7 @@
         <v>400</v>
       </c>
       <c r="S16" t="n">
-        <v>400</v>
+        <v>360.2679223258062</v>
       </c>
       <c r="T16" t="n">
         <v>400</v>
@@ -28608,7 +28608,7 @@
         <v>400</v>
       </c>
       <c r="Y16" t="n">
-        <v>400</v>
+        <v>383.2675058894555</v>
       </c>
     </row>
     <row r="17">
@@ -28633,7 +28633,7 @@
         <v>404</v>
       </c>
       <c r="G17" t="n">
-        <v>404</v>
+        <v>404.0000000000043</v>
       </c>
       <c r="H17" t="n">
         <v>404</v>
@@ -28697,7 +28697,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>384.5565566463266</v>
+        <v>25.55655664631732</v>
       </c>
       <c r="C18" t="n">
         <v>361.0999124455193</v>
@@ -28745,10 +28745,10 @@
         <v>154.6833405621777</v>
       </c>
       <c r="R18" t="n">
-        <v>179.3261369150208</v>
+        <v>404</v>
       </c>
       <c r="S18" t="n">
-        <v>404</v>
+        <v>371.0736309025402</v>
       </c>
       <c r="T18" t="n">
         <v>404</v>
@@ -28757,16 +28757,16 @@
         <v>400.2008786281113</v>
       </c>
       <c r="V18" t="n">
-        <v>236.7474939874914</v>
+        <v>404</v>
       </c>
       <c r="W18" t="n">
         <v>404</v>
       </c>
       <c r="X18" t="n">
-        <v>60.86273944538755</v>
+        <v>60.86273944537831</v>
       </c>
       <c r="Y18" t="n">
-        <v>40.39139276613435</v>
+        <v>40.39139276612511</v>
       </c>
     </row>
     <row r="19">
@@ -28779,25 +28779,25 @@
         <v>404</v>
       </c>
       <c r="C19" t="n">
-        <v>272.7252466480447</v>
+        <v>404</v>
       </c>
       <c r="D19" t="n">
-        <v>285.5362180555555</v>
+        <v>404</v>
       </c>
       <c r="E19" t="n">
-        <v>280.9809048369565</v>
+        <v>404</v>
       </c>
       <c r="F19" t="n">
-        <v>274.3828559677419</v>
+        <v>404</v>
       </c>
       <c r="G19" t="n">
-        <v>404</v>
+        <v>366.0784158556263</v>
       </c>
       <c r="H19" t="n">
-        <v>404</v>
+        <v>227.6969293803072</v>
       </c>
       <c r="I19" t="n">
-        <v>404</v>
+        <v>173.0000785709379</v>
       </c>
       <c r="J19" t="n">
         <v>26.72699801623563</v>
@@ -28827,25 +28827,25 @@
         <v>404</v>
       </c>
       <c r="S19" t="n">
+        <v>360.2679223258062</v>
+      </c>
+      <c r="T19" t="n">
         <v>404</v>
-      </c>
-      <c r="T19" t="n">
-        <v>209.508336998061</v>
       </c>
       <c r="U19" t="n">
         <v>404</v>
       </c>
       <c r="V19" t="n">
-        <v>199.1703102162162</v>
+        <v>404</v>
       </c>
       <c r="W19" t="n">
-        <v>366.0212815283816</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X19" t="n">
-        <v>404</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y19" t="n">
-        <v>404</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="20">
@@ -28870,7 +28870,7 @@
         <v>404</v>
       </c>
       <c r="G20" t="n">
-        <v>404.0000000000075</v>
+        <v>404.0000000000068</v>
       </c>
       <c r="H20" t="n">
         <v>404</v>
@@ -28937,16 +28937,16 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C21" t="n">
-        <v>361.0999124455193</v>
+        <v>2.099912445509986</v>
       </c>
       <c r="D21" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>325.5954226674802</v>
@@ -28955,7 +28955,7 @@
         <v>330.7762569977419</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>212.1645934385184</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -28979,16 +28979,16 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>154.6833405621777</v>
       </c>
       <c r="R21" t="n">
-        <v>179.3261369150208</v>
+        <v>356.510299583489</v>
       </c>
       <c r="S21" t="n">
-        <v>104.8871603419698</v>
+        <v>404</v>
       </c>
       <c r="T21" t="n">
-        <v>200.5710070916053</v>
+        <v>404</v>
       </c>
       <c r="U21" t="n">
         <v>400.2008786281113</v>
@@ -29013,7 +29013,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>287.1138003370787</v>
+        <v>404</v>
       </c>
       <c r="C22" t="n">
         <v>404</v>
@@ -29022,13 +29022,13 @@
         <v>404</v>
       </c>
       <c r="E22" t="n">
-        <v>280.9809048369565</v>
+        <v>398.5459778387044</v>
       </c>
       <c r="F22" t="n">
         <v>274.3828559677419</v>
       </c>
       <c r="G22" t="n">
-        <v>404</v>
+        <v>244.9230531693989</v>
       </c>
       <c r="H22" t="n">
         <v>227.6969293803072</v>
@@ -29067,7 +29067,7 @@
         <v>360.2679223258062</v>
       </c>
       <c r="T22" t="n">
-        <v>404</v>
+        <v>209.508336998061</v>
       </c>
       <c r="U22" t="n">
         <v>404</v>
@@ -29076,7 +29076,7 @@
         <v>404</v>
       </c>
       <c r="W22" t="n">
-        <v>284.8826628321287</v>
+        <v>404</v>
       </c>
       <c r="X22" t="n">
         <v>404</v>
@@ -29107,7 +29107,7 @@
         <v>404</v>
       </c>
       <c r="G23" t="n">
-        <v>404.0000000000061</v>
+        <v>404</v>
       </c>
       <c r="H23" t="n">
         <v>404</v>
@@ -29174,16 +29174,16 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C24" t="n">
-        <v>361.0999124455193</v>
+        <v>297.2823092509113</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>325.5954226674802</v>
@@ -29222,19 +29222,19 @@
         <v>404</v>
       </c>
       <c r="S24" t="n">
-        <v>348.0525602465511</v>
+        <v>404</v>
       </c>
       <c r="T24" t="n">
         <v>404</v>
       </c>
       <c r="U24" t="n">
-        <v>41.20087862811128</v>
+        <v>400.2008786281113</v>
       </c>
       <c r="V24" t="n">
-        <v>55.51066719152016</v>
+        <v>404</v>
       </c>
       <c r="W24" t="n">
-        <v>73.37314290982852</v>
+        <v>404</v>
       </c>
       <c r="X24" t="n">
         <v>404</v>
@@ -29250,7 +29250,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>404</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C25" t="n">
         <v>272.7252466480447</v>
@@ -29262,19 +29262,19 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F25" t="n">
-        <v>274.3828559677419</v>
+        <v>404</v>
       </c>
       <c r="G25" t="n">
         <v>404</v>
       </c>
       <c r="H25" t="n">
-        <v>227.6969293803072</v>
+        <v>404</v>
       </c>
       <c r="I25" t="n">
-        <v>173.0000785709379</v>
+        <v>286.2233943105978</v>
       </c>
       <c r="J25" t="n">
-        <v>385.7269980162357</v>
+        <v>26.72699801623563</v>
       </c>
       <c r="K25" t="n">
         <v>274.4837246208152</v>
@@ -29301,25 +29301,25 @@
         <v>404</v>
       </c>
       <c r="S25" t="n">
-        <v>360.2679223258062</v>
+        <v>404</v>
       </c>
       <c r="T25" t="n">
-        <v>398.1491051944232</v>
+        <v>404</v>
       </c>
       <c r="U25" t="n">
-        <v>150.9518011105235</v>
+        <v>404</v>
       </c>
       <c r="V25" t="n">
-        <v>199.1703102162162</v>
+        <v>404</v>
       </c>
       <c r="W25" t="n">
-        <v>404</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X25" t="n">
-        <v>404</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y25" t="n">
-        <v>404</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="26">
@@ -29411,7 +29411,7 @@
         <v>356</v>
       </c>
       <c r="C27" t="n">
-        <v>356</v>
+        <v>11.09991244549595</v>
       </c>
       <c r="D27" t="n">
         <v>347.9376868977026</v>
@@ -29459,13 +29459,13 @@
         <v>356</v>
       </c>
       <c r="S27" t="n">
-        <v>113.8871603419698</v>
+        <v>317.3083105294957</v>
       </c>
       <c r="T27" t="n">
-        <v>54.77688785902325</v>
+        <v>54.77688785899986</v>
       </c>
       <c r="U27" t="n">
-        <v>214.5210626329985</v>
+        <v>356</v>
       </c>
       <c r="V27" t="n">
         <v>356</v>
@@ -29490,25 +29490,25 @@
         <v>356</v>
       </c>
       <c r="C28" t="n">
-        <v>356</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D28" t="n">
         <v>356</v>
       </c>
       <c r="E28" t="n">
-        <v>356</v>
+        <v>319.4816294502437</v>
       </c>
       <c r="F28" t="n">
         <v>356</v>
       </c>
       <c r="G28" t="n">
-        <v>356</v>
+        <v>244.9230531693989</v>
       </c>
       <c r="H28" t="n">
         <v>356</v>
       </c>
       <c r="I28" t="n">
-        <v>193.664576418225</v>
+        <v>356</v>
       </c>
       <c r="J28" t="n">
         <v>26.72699801623563</v>
@@ -29556,7 +29556,7 @@
         <v>356</v>
       </c>
       <c r="Y28" t="n">
-        <v>287.4653528494624</v>
+        <v>356</v>
       </c>
     </row>
     <row r="29">
@@ -29648,7 +29648,7 @@
         <v>362</v>
       </c>
       <c r="C30" t="n">
-        <v>361.0999124455193</v>
+        <v>160.1259612702518</v>
       </c>
       <c r="D30" t="n">
         <v>347.9376868977026</v>
@@ -29663,7 +29663,7 @@
         <v>325.5954226674802</v>
       </c>
       <c r="H30" t="n">
-        <v>330.7762569977419</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -29693,19 +29693,19 @@
         <v>154.6833405621777</v>
       </c>
       <c r="R30" t="n">
-        <v>188.3261369150208</v>
+        <v>362</v>
       </c>
       <c r="S30" t="n">
         <v>362</v>
       </c>
       <c r="T30" t="n">
-        <v>54.77688785902325</v>
+        <v>362</v>
       </c>
       <c r="U30" t="n">
         <v>362</v>
       </c>
       <c r="V30" t="n">
-        <v>311.1467670529464</v>
+        <v>362</v>
       </c>
       <c r="W30" t="n">
         <v>362</v>
@@ -29724,34 +29724,34 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>287.1138003370787</v>
+        <v>362</v>
       </c>
       <c r="C31" t="n">
         <v>272.7252466480447</v>
       </c>
       <c r="D31" t="n">
-        <v>285.5362180555555</v>
+        <v>362</v>
       </c>
       <c r="E31" t="n">
         <v>280.9809048369565</v>
       </c>
       <c r="F31" t="n">
-        <v>274.3828559677419</v>
+        <v>362</v>
       </c>
       <c r="G31" t="n">
         <v>362</v>
       </c>
       <c r="H31" t="n">
+        <v>227.6969293803072</v>
+      </c>
+      <c r="I31" t="n">
+        <v>173.0000785709379</v>
+      </c>
+      <c r="J31" t="n">
+        <v>116.2054147942984</v>
+      </c>
+      <c r="K31" t="n">
         <v>362</v>
-      </c>
-      <c r="I31" t="n">
-        <v>362</v>
-      </c>
-      <c r="J31" t="n">
-        <v>329.5476610761801</v>
-      </c>
-      <c r="K31" t="n">
-        <v>274.4837246208152</v>
       </c>
       <c r="L31" t="n">
         <v>362</v>
@@ -29787,13 +29787,13 @@
         <v>362</v>
       </c>
       <c r="W31" t="n">
-        <v>226.3728098387097</v>
+        <v>362</v>
       </c>
       <c r="X31" t="n">
         <v>362</v>
       </c>
       <c r="Y31" t="n">
-        <v>287.4653528494624</v>
+        <v>362</v>
       </c>
     </row>
     <row r="32">
@@ -29900,7 +29900,7 @@
         <v>325.5954226674802</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>330.7762569977419</v>
       </c>
       <c r="I33" t="n">
         <v>212.1645934385184</v>
@@ -29930,22 +29930,22 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>194.3261369150208</v>
+        <v>410</v>
       </c>
       <c r="S33" t="n">
         <v>410</v>
       </c>
       <c r="T33" t="n">
-        <v>60.77688785902325</v>
+        <v>404.7768878590232</v>
       </c>
       <c r="U33" t="n">
-        <v>400.2008786281113</v>
+        <v>56.20087862811128</v>
       </c>
       <c r="V33" t="n">
-        <v>410</v>
+        <v>70.51066719152016</v>
       </c>
       <c r="W33" t="n">
-        <v>339.0981074486257</v>
+        <v>132.1373201743846</v>
       </c>
       <c r="X33" t="n">
         <v>410</v>
@@ -29961,13 +29961,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>287.1138003370787</v>
+        <v>410</v>
       </c>
       <c r="C34" t="n">
-        <v>272.7252466480447</v>
+        <v>410</v>
       </c>
       <c r="D34" t="n">
-        <v>285.5362180555555</v>
+        <v>410</v>
       </c>
       <c r="E34" t="n">
         <v>280.9809048369565</v>
@@ -29979,19 +29979,19 @@
         <v>244.9230531693989</v>
       </c>
       <c r="H34" t="n">
+        <v>227.6969293803072</v>
+      </c>
+      <c r="I34" t="n">
+        <v>199.8020230591895</v>
+      </c>
+      <c r="J34" t="n">
+        <v>26.72699801623563</v>
+      </c>
+      <c r="K34" t="n">
+        <v>274.4837246208152</v>
+      </c>
+      <c r="L34" t="n">
         <v>410</v>
-      </c>
-      <c r="I34" t="n">
-        <v>173.0000785709379</v>
-      </c>
-      <c r="J34" t="n">
-        <v>370.7269980162357</v>
-      </c>
-      <c r="K34" t="n">
-        <v>345.1134784929254</v>
-      </c>
-      <c r="L34" t="n">
-        <v>405.5850379938448</v>
       </c>
       <c r="M34" t="n">
         <v>410</v>
@@ -30015,10 +30015,10 @@
         <v>360.2679223258062</v>
       </c>
       <c r="T34" t="n">
+        <v>209.508336998061</v>
+      </c>
+      <c r="U34" t="n">
         <v>410</v>
-      </c>
-      <c r="U34" t="n">
-        <v>150.9518011105235</v>
       </c>
       <c r="V34" t="n">
         <v>410</v>
@@ -30030,7 +30030,7 @@
         <v>410</v>
       </c>
       <c r="Y34" t="n">
-        <v>287.4653528494624</v>
+        <v>410</v>
       </c>
     </row>
     <row r="35">
@@ -30128,10 +30128,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>5.672097221912622</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>2.636242337876865</v>
       </c>
       <c r="G36" t="n">
         <v>325.5954226674802</v>
@@ -30140,7 +30140,7 @@
         <v>330.7762569977419</v>
       </c>
       <c r="I36" t="n">
-        <v>212.1645934385184</v>
+        <v>148.652043889402</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30167,19 +30167,19 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>413</v>
+        <v>201.3261369150208</v>
       </c>
       <c r="S36" t="n">
         <v>413</v>
       </c>
       <c r="T36" t="n">
-        <v>128.0798080334076</v>
+        <v>404.7768878590232</v>
       </c>
       <c r="U36" t="n">
-        <v>63.20087862811128</v>
+        <v>400.2008786281113</v>
       </c>
       <c r="V36" t="n">
-        <v>77.51066719152016</v>
+        <v>413</v>
       </c>
       <c r="W36" t="n">
         <v>413</v>
@@ -30198,13 +30198,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>287.1138003370787</v>
+        <v>413</v>
       </c>
       <c r="C37" t="n">
-        <v>413</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D37" t="n">
-        <v>413</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E37" t="n">
         <v>413</v>
@@ -30216,10 +30216,10 @@
         <v>413</v>
       </c>
       <c r="H37" t="n">
-        <v>247.2217610345276</v>
+        <v>413</v>
       </c>
       <c r="I37" t="n">
-        <v>173.0000785709379</v>
+        <v>413</v>
       </c>
       <c r="J37" t="n">
         <v>26.72699801623563</v>
@@ -30228,7 +30228,7 @@
         <v>274.4837246208152</v>
       </c>
       <c r="L37" t="n">
-        <v>405.5850379938448</v>
+        <v>413</v>
       </c>
       <c r="M37" t="n">
         <v>413</v>
@@ -30249,10 +30249,10 @@
         <v>413</v>
       </c>
       <c r="S37" t="n">
-        <v>413</v>
+        <v>360.2679223258062</v>
       </c>
       <c r="T37" t="n">
-        <v>413</v>
+        <v>255.4838339177354</v>
       </c>
       <c r="U37" t="n">
         <v>150.9518011105235</v>
@@ -30261,13 +30261,13 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W37" t="n">
-        <v>413</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X37" t="n">
         <v>413</v>
       </c>
       <c r="Y37" t="n">
-        <v>287.4653528494624</v>
+        <v>413</v>
       </c>
     </row>
     <row r="38">
@@ -30365,16 +30365,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>5.672097221912622</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>2.636242337876865</v>
       </c>
       <c r="G39" t="n">
         <v>325.5954226674802</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>55.58984436364636</v>
       </c>
       <c r="I39" t="n">
         <v>212.1645934385184</v>
@@ -30413,10 +30413,10 @@
         <v>404.7768878590232</v>
       </c>
       <c r="U39" t="n">
-        <v>117.2800558002376</v>
+        <v>400.2008786281113</v>
       </c>
       <c r="V39" t="n">
-        <v>77.51066719152016</v>
+        <v>413</v>
       </c>
       <c r="W39" t="n">
         <v>413</v>
@@ -30435,7 +30435,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>413</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C40" t="n">
         <v>272.7252466480447</v>
@@ -30447,22 +30447,22 @@
         <v>413</v>
       </c>
       <c r="F40" t="n">
-        <v>274.3828559677419</v>
+        <v>413</v>
       </c>
       <c r="G40" t="n">
-        <v>244.9230531693989</v>
+        <v>413</v>
       </c>
       <c r="H40" t="n">
-        <v>227.6969293803072</v>
+        <v>413</v>
       </c>
       <c r="I40" t="n">
         <v>173.0000785709379</v>
       </c>
       <c r="J40" t="n">
-        <v>363.7269980162357</v>
+        <v>26.72699801623563</v>
       </c>
       <c r="K40" t="n">
-        <v>274.4837246208152</v>
+        <v>413</v>
       </c>
       <c r="L40" t="n">
         <v>405.5850379938448</v>
@@ -30486,25 +30486,25 @@
         <v>413</v>
       </c>
       <c r="S40" t="n">
-        <v>408.1985842181757</v>
+        <v>413</v>
       </c>
       <c r="T40" t="n">
-        <v>209.508336998061</v>
+        <v>413</v>
       </c>
       <c r="U40" t="n">
-        <v>150.9518011105235</v>
+        <v>413</v>
       </c>
       <c r="V40" t="n">
-        <v>413</v>
+        <v>252.7496770096652</v>
       </c>
       <c r="W40" t="n">
-        <v>413</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X40" t="n">
-        <v>413</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y40" t="n">
-        <v>413</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="41">
@@ -30605,13 +30605,13 @@
         <v>313</v>
       </c>
       <c r="F42" t="n">
-        <v>313</v>
+        <v>215.7735812715559</v>
       </c>
       <c r="G42" t="n">
         <v>313</v>
       </c>
       <c r="H42" t="n">
-        <v>215.7735812715559</v>
+        <v>313</v>
       </c>
       <c r="I42" t="n">
         <v>212.1645934385184</v>
@@ -30690,10 +30690,10 @@
         <v>313</v>
       </c>
       <c r="H43" t="n">
+        <v>313</v>
+      </c>
+      <c r="I43" t="n">
         <v>307.8659044299907</v>
-      </c>
-      <c r="I43" t="n">
-        <v>313</v>
       </c>
       <c r="J43" t="n">
         <v>313</v>
@@ -34743,16 +34743,16 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="K2" t="n">
         <v>34.26191457286433</v>
       </c>
       <c r="L2" t="n">
-        <v>42.50493467336685</v>
+        <v>259.3129505030946</v>
       </c>
       <c r="M2" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>346</v>
@@ -34761,10 +34761,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
+        <v>38.44533694424321</v>
+      </c>
+      <c r="Q2" t="n">
         <v>346</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>255.2533527739708</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34828,7 +34828,7 @@
         <v>214.3749772823007</v>
       </c>
       <c r="L3" t="n">
-        <v>304.3175186776174</v>
+        <v>304.3175186775915</v>
       </c>
       <c r="M3" t="n">
         <v>123.4650421645043</v>
@@ -34889,7 +34889,7 @@
         <v>126.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>132.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -34898,16 +34898,16 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>105.8779034524467</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>132.5162753791848</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.414962006155235</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34934,7 +34934,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>95.37772092432513</v>
+        <v>256.0481988894765</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -34980,7 +34980,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>216.8080158297277</v>
       </c>
       <c r="K5" t="n">
         <v>34.26191457286433</v>
@@ -34995,13 +34995,13 @@
         <v>346</v>
       </c>
       <c r="O5" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>38.44533694424321</v>
       </c>
       <c r="Q5" t="n">
-        <v>216.8080158297276</v>
+        <v>346</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35114,13 +35114,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>119.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>9.340708886010749</v>
       </c>
       <c r="E7" t="n">
         <v>126.0190951630435</v>
@@ -35129,16 +35129,16 @@
         <v>132.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>162.0769468306011</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>179.3030706196928</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>233.9999214290621</v>
       </c>
       <c r="J7" t="n">
-        <v>149.4648964272462</v>
+        <v>346</v>
       </c>
       <c r="K7" t="n">
         <v>132.5162753791848</v>
@@ -35168,13 +35168,13 @@
         <v>46.73207767419376</v>
       </c>
       <c r="T7" t="n">
-        <v>197.491663001939</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>256.0481988894765</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>207.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -35217,7 +35217,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>352</v>
+        <v>352.000000000006</v>
       </c>
       <c r="K8" t="n">
         <v>34.26191457286433</v>
@@ -35226,10 +35226,10 @@
         <v>42.50493467336685</v>
       </c>
       <c r="M8" t="n">
-        <v>352</v>
+        <v>352.000000000006</v>
       </c>
       <c r="N8" t="n">
-        <v>352</v>
+        <v>352.000000000006</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -35238,7 +35238,7 @@
         <v>38.44533694424321</v>
       </c>
       <c r="Q8" t="n">
-        <v>222.5655915873034</v>
+        <v>222.5655915872852</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35372,13 +35372,13 @@
         <v>179.3030706196928</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>233.9999214290621</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>43.62763473511953</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35402,7 +35402,7 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>46.73207767419375</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -35414,10 +35414,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>71.33912392009535</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>159.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>119.5346471505376</v>
@@ -35454,28 +35454,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>359.0000000000137</v>
       </c>
       <c r="K11" t="n">
-        <v>34.26191457286432</v>
+        <v>34.26191457286433</v>
       </c>
       <c r="L11" t="n">
-        <v>42.50493467336684</v>
+        <v>42.50493467336685</v>
       </c>
       <c r="M11" t="n">
-        <v>229.2827633044749</v>
+        <v>359.0000000000137</v>
       </c>
       <c r="N11" t="n">
-        <v>359</v>
+        <v>359.0000000000137</v>
       </c>
       <c r="O11" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>38.44533694424321</v>
       </c>
       <c r="Q11" t="n">
-        <v>359</v>
+        <v>229.2827633044341</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35594,16 +35594,16 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>62.37362768705785</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>155.0769468306011</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -35639,7 +35639,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>39.73207767419375</v>
+        <v>39.73207767419376</v>
       </c>
       <c r="T13" t="n">
         <v>190.491663001939</v>
@@ -35651,10 +35651,10 @@
         <v>200.8296897837838</v>
       </c>
       <c r="W13" t="n">
-        <v>107.8630815553814</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y13" t="n">
         <v>112.5346471505376</v>
@@ -35691,19 +35691,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>359.0000000000092</v>
       </c>
       <c r="K14" t="n">
-        <v>34.26191457286432</v>
+        <v>34.26191457286433</v>
       </c>
       <c r="L14" t="n">
-        <v>359</v>
+        <v>271.7876979778147</v>
       </c>
       <c r="M14" t="n">
-        <v>359</v>
+        <v>359.0000000000092</v>
       </c>
       <c r="N14" t="n">
-        <v>359</v>
+        <v>359.0000000000092</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -35712,7 +35712,7 @@
         <v>38.44533694424321</v>
       </c>
       <c r="Q14" t="n">
-        <v>271.7876979778419</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35825,19 +35825,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>64.03123700675503</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F16" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -35852,7 +35852,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>125.5162753791848</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -35876,7 +35876,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>39.73207767419376</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>190.491663001939</v>
@@ -35894,7 +35894,7 @@
         <v>152.5563545698924</v>
       </c>
       <c r="Y16" t="n">
-        <v>112.5346471505376</v>
+        <v>95.80215303999317</v>
       </c>
     </row>
     <row r="17">
@@ -35919,7 +35919,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5119744466521314</v>
+        <v>0.5119744466564515</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -35931,16 +35931,16 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>359</v>
+        <v>34.26191457286432</v>
       </c>
       <c r="L17" t="n">
-        <v>42.50493467336685</v>
+        <v>271.7876979778142</v>
       </c>
       <c r="M17" t="n">
-        <v>359</v>
+        <v>359.0000000000093</v>
       </c>
       <c r="N17" t="n">
-        <v>263.5446778773393</v>
+        <v>359.0000000000093</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -35949,7 +35949,7 @@
         <v>38.44533694424321</v>
       </c>
       <c r="Q17" t="n">
-        <v>359</v>
+        <v>359.0000000000093</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36065,25 +36065,25 @@
         <v>116.8861996629213</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>131.2747533519553</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>118.4637819444445</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>123.0190951630435</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>129.6171440322581</v>
       </c>
       <c r="G19" t="n">
-        <v>159.0769468306011</v>
+        <v>121.1553626862274</v>
       </c>
       <c r="H19" t="n">
-        <v>176.3030706196928</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>230.9999214290621</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -36113,25 +36113,25 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>43.73207767419375</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>194.491663001939</v>
       </c>
       <c r="U19" t="n">
         <v>253.0481988894765</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>204.8296897837838</v>
       </c>
       <c r="W19" t="n">
-        <v>139.6484716896719</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>156.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>116.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -36156,7 +36156,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5119744466596348</v>
+        <v>0.5119744466589526</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -36165,28 +36165,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>359.0000000000093</v>
       </c>
       <c r="K20" t="n">
-        <v>34.26191457286432</v>
+        <v>358.9999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>42.50493467336684</v>
+        <v>42.50493467336685</v>
       </c>
       <c r="M20" t="n">
-        <v>359</v>
+        <v>263.5446778773209</v>
       </c>
       <c r="N20" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>38.44533694424321</v>
       </c>
       <c r="Q20" t="n">
-        <v>229.2827633044749</v>
+        <v>359.0000000000093</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36299,7 +36299,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>116.8861996629213</v>
       </c>
       <c r="C22" t="n">
         <v>131.2747533519553</v>
@@ -36308,13 +36308,13 @@
         <v>118.4637819444445</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>117.5650730017479</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>159.0769468306011</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -36353,7 +36353,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>194.491663001939</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
         <v>253.0481988894765</v>
@@ -36362,7 +36362,7 @@
         <v>204.8296897837838</v>
       </c>
       <c r="W22" t="n">
-        <v>58.50985299341907</v>
+        <v>177.6271901612903</v>
       </c>
       <c r="X22" t="n">
         <v>156.5563545698924</v>
@@ -36393,7 +36393,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5119744466582705</v>
+        <v>0.5119744466521314</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -36405,16 +36405,16 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
+        <v>34.26191457286432</v>
+      </c>
+      <c r="L23" t="n">
         <v>359</v>
       </c>
-      <c r="L23" t="n">
-        <v>306.0496125507061</v>
-      </c>
       <c r="M23" t="n">
-        <v>359</v>
+        <v>359.0000000000105</v>
       </c>
       <c r="N23" t="n">
-        <v>359</v>
+        <v>271.7876979778212</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -36423,7 +36423,7 @@
         <v>38.44533694424321</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>359.0000000000105</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36536,7 +36536,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>116.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -36548,19 +36548,19 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>129.6171440322581</v>
       </c>
       <c r="G25" t="n">
         <v>159.0769468306011</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>176.3030706196928</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>113.2233157396598</v>
       </c>
       <c r="J25" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -36587,25 +36587,25 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>43.73207767419375</v>
       </c>
       <c r="T25" t="n">
-        <v>188.6407681963622</v>
+        <v>194.491663001939</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>253.0481988894765</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>204.8296897837838</v>
       </c>
       <c r="W25" t="n">
-        <v>177.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>156.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>116.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -36639,28 +36639,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>350.0000000000234</v>
       </c>
       <c r="K26" t="n">
-        <v>34.26191457286432</v>
+        <v>293.3536511851489</v>
       </c>
       <c r="L26" t="n">
-        <v>42.50493467336683</v>
+        <v>42.50493467336685</v>
       </c>
       <c r="M26" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>220.6463996681115</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>38.44533694424321</v>
+        <v>350.0000000000234</v>
       </c>
       <c r="Q26" t="n">
-        <v>350</v>
+        <v>350.0000000000234</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36776,25 +36776,25 @@
         <v>68.88619966292134</v>
       </c>
       <c r="C28" t="n">
-        <v>83.27475335195533</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>70.46378194444452</v>
       </c>
       <c r="E28" t="n">
-        <v>75.01909516304346</v>
+        <v>38.50072461328715</v>
       </c>
       <c r="F28" t="n">
         <v>81.61714403225807</v>
       </c>
       <c r="G28" t="n">
-        <v>111.0769468306011</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>128.3030706196928</v>
       </c>
       <c r="I28" t="n">
-        <v>20.66449784728701</v>
+        <v>182.9999214290621</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -36842,7 +36842,7 @@
         <v>108.5563545698924</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>68.53464715053764</v>
       </c>
     </row>
     <row r="29">
@@ -36879,25 +36879,25 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>34.26191457286432</v>
+        <v>254.9083142409235</v>
       </c>
       <c r="L29" t="n">
-        <v>42.50493467336683</v>
+        <v>42.50493467336685</v>
       </c>
       <c r="M29" t="n">
-        <v>350</v>
+        <v>350.0000000000175</v>
       </c>
       <c r="N29" t="n">
-        <v>259.0917366123547</v>
+        <v>350.0000000000175</v>
       </c>
       <c r="O29" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>350</v>
+        <v>38.44533694424321</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>350.0000000000175</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37010,34 +37010,34 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>74.88619966292134</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>76.46378194444452</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>87.61714403225807</v>
       </c>
       <c r="G31" t="n">
         <v>117.0769468306011</v>
       </c>
       <c r="H31" t="n">
-        <v>134.3030706196928</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>188.9999214290621</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>302.8206630599445</v>
+        <v>89.47841677806279</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>87.51627537918483</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -37073,13 +37073,13 @@
         <v>162.8296897837838</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>135.6271901612903</v>
       </c>
       <c r="X31" t="n">
         <v>114.5563545698924</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>74.53464715053764</v>
       </c>
     </row>
     <row r="32">
@@ -37113,22 +37113,22 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>34.26191457286432</v>
+      </c>
+      <c r="L32" t="n">
+        <v>257.3937585839027</v>
+      </c>
+      <c r="M32" t="n">
         <v>344</v>
       </c>
-      <c r="K32" t="n">
-        <v>34.26191457286433</v>
-      </c>
-      <c r="L32" t="n">
-        <v>42.50493467336685</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
       <c r="N32" t="n">
-        <v>214.8888239105358</v>
+        <v>344</v>
       </c>
       <c r="O32" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
         <v>38.44533694424321</v>
@@ -37198,7 +37198,7 @@
         <v>214.3749772823007</v>
       </c>
       <c r="L33" t="n">
-        <v>296.3983267583996</v>
+        <v>305.3822715751021</v>
       </c>
       <c r="M33" t="n">
         <v>123.4650421645043</v>
@@ -37207,7 +37207,7 @@
         <v>172.1079935048813</v>
       </c>
       <c r="O33" t="n">
-        <v>275.7452200159539</v>
+        <v>266.7612751992514</v>
       </c>
       <c r="P33" t="n">
         <v>141.1853064014457</v>
@@ -37247,13 +37247,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>122.8861996629213</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>137.2747533519553</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>124.4637819444445</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -37265,19 +37265,19 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>182.3030706196928</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>26.8019444882515</v>
       </c>
       <c r="J34" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>70.62975387211024</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>4.414962006155253</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -37301,10 +37301,10 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>200.491663001939</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>259.0481988894765</v>
       </c>
       <c r="V34" t="n">
         <v>210.8296897837838</v>
@@ -37316,7 +37316,7 @@
         <v>162.5563545698924</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>122.5346471505376</v>
       </c>
     </row>
     <row r="35">
@@ -37356,13 +37356,13 @@
         <v>337</v>
       </c>
       <c r="L35" t="n">
-        <v>284.9385014395953</v>
+        <v>42.50493467336685</v>
       </c>
       <c r="M35" t="n">
         <v>337</v>
       </c>
       <c r="N35" t="n">
-        <v>337</v>
+        <v>242.4335667662284</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -37371,7 +37371,7 @@
         <v>38.44533694424321</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37484,13 +37484,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>125.8861996629213</v>
       </c>
       <c r="C37" t="n">
-        <v>140.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>127.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
         <v>132.0190951630435</v>
@@ -37502,10 +37502,10 @@
         <v>168.0769468306011</v>
       </c>
       <c r="H37" t="n">
-        <v>19.52483165422049</v>
+        <v>185.3030706196928</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>239.9999214290621</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>7.414962006155253</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37535,10 +37535,10 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>52.73207767419375</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>203.491663001939</v>
+        <v>45.97549691967436</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -37547,13 +37547,13 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>186.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>165.5563545698924</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>125.5346471505376</v>
       </c>
     </row>
     <row r="38">
@@ -37587,28 +37587,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="K38" t="n">
-        <v>34.26191457286431</v>
+        <v>34.26191457286433</v>
       </c>
       <c r="L38" t="n">
-        <v>42.50493467336683</v>
+        <v>42.50493467336685</v>
       </c>
       <c r="M38" t="n">
-        <v>246.6169891376072</v>
+        <v>337</v>
       </c>
       <c r="N38" t="n">
         <v>337</v>
       </c>
       <c r="O38" t="n">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>337</v>
+        <v>38.44533694424321</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>208.171652193364</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37672,7 +37672,7 @@
         <v>214.3749772823007</v>
       </c>
       <c r="L39" t="n">
-        <v>268.6811550412279</v>
+        <v>305.3822715751021</v>
       </c>
       <c r="M39" t="n">
         <v>123.4650421645043</v>
@@ -37681,7 +37681,7 @@
         <v>172.1079935048813</v>
       </c>
       <c r="O39" t="n">
-        <v>275.7452200159539</v>
+        <v>239.0441034820797</v>
       </c>
       <c r="P39" t="n">
         <v>141.1853064014457</v>
@@ -37721,7 +37721,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>125.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -37733,22 +37733,22 @@
         <v>132.0190951630435</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>138.6171440322581</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>168.0769468306011</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>185.3030706196928</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>138.5162753791848</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -37772,25 +37772,25 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>47.93066189236943</v>
+        <v>52.73207767419376</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>203.491663001939</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>262.0481988894765</v>
       </c>
       <c r="V40" t="n">
-        <v>213.8296897837838</v>
+        <v>53.579366793449</v>
       </c>
       <c r="W40" t="n">
-        <v>186.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>165.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>125.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -37833,19 +37833,19 @@
         <v>42.50493467336685</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="N41" t="n">
-        <v>246.6169891376072</v>
+        <v>337</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>337</v>
+        <v>38.44533694424321</v>
       </c>
       <c r="Q41" t="n">
-        <v>337</v>
+        <v>208.171652193364</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37903,7 +37903,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>138.8241439735248</v>
+        <v>102.1230274396506</v>
       </c>
       <c r="K42" t="n">
         <v>214.3749772823007</v>
@@ -37921,7 +37921,7 @@
         <v>275.7452200159539</v>
       </c>
       <c r="P42" t="n">
-        <v>104.4841898675713</v>
+        <v>141.1853064014457</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -37976,10 +37976,10 @@
         <v>68.07694683060112</v>
       </c>
       <c r="H43" t="n">
-        <v>80.16897504968357</v>
+        <v>85.30307061969286</v>
       </c>
       <c r="I43" t="n">
-        <v>139.9999214290621</v>
+        <v>134.8658258590526</v>
       </c>
       <c r="J43" t="n">
         <v>286.2730019837644</v>
@@ -38064,10 +38064,10 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>242.4335667662284</v>
+        <v>34.26191457286431</v>
       </c>
       <c r="L44" t="n">
-        <v>42.50493467336685</v>
+        <v>250.6765868667309</v>
       </c>
       <c r="M44" t="n">
         <v>337</v>
@@ -38140,7 +38140,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>138.8241439735248</v>
+        <v>102.1230274396506</v>
       </c>
       <c r="K45" t="n">
         <v>214.3749772823007</v>
@@ -38158,7 +38158,7 @@
         <v>275.7452200159539</v>
       </c>
       <c r="P45" t="n">
-        <v>104.4841898675713</v>
+        <v>141.1853064014457</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
